--- a/public/databases/iconic-venues.xlsx
+++ b/public/databases/iconic-venues.xlsx
@@ -4,7 +4,13 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="Formula 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Football Stadiums" sheetId="2" r:id="rId2"/>
+    <sheet name="Football" sheetId="2" r:id="rId2"/>
+    <sheet name="Cricket" sheetId="3" r:id="rId3"/>
+    <sheet name="Tennis" sheetId="4" r:id="rId4"/>
+    <sheet name="Golf" sheetId="5" r:id="rId5"/>
+    <sheet name="Rugby" sheetId="6" r:id="rId6"/>
+    <sheet name="Olympic Venues" sheetId="7" r:id="rId7"/>
+    <sheet name="Boxing" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -398,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X2"/>
+  <dimension ref="A1:Q4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,60 +423,39 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
-        <v>countryFlag</v>
+        <v>opened</v>
       </c>
       <c r="G1" t="str">
-        <v>opened</v>
+        <v>capacity</v>
       </c>
       <c r="H1" t="str">
-        <v>capacity</v>
+        <v>lat</v>
       </c>
       <c r="I1" t="str">
-        <v>lat</v>
+        <v>lng</v>
       </c>
       <c r="J1" t="str">
-        <v>lng</v>
+        <v>architect</v>
       </c>
       <c r="K1" t="str">
-        <v>architect</v>
+        <v>surface</v>
       </c>
       <c r="L1" t="str">
-        <v>surface</v>
+        <v>raceDistance</v>
       </c>
       <c r="M1" t="str">
-        <v>themePrimary</v>
+        <v>numberOfTurns</v>
       </c>
       <c r="N1" t="str">
-        <v>themeSecondary</v>
+        <v>nickname</v>
       </c>
       <c r="O1" t="str">
-        <v>themeAccent</v>
+        <v>famousFor</v>
       </c>
       <c r="P1" t="str">
-        <v>famousFor</v>
+        <v>iconicMoments</v>
       </c>
       <c r="Q1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="R1" t="str">
-        <v>raceDistance</v>
-      </c>
-      <c r="S1" t="str">
-        <v>numberOfTurns</v>
-      </c>
-      <c r="T1" t="str">
-        <v>altitude</v>
-      </c>
-      <c r="U1" t="str">
-        <v>nickname</v>
-      </c>
-      <c r="V1" t="str">
-        <v>notableEvents</v>
-      </c>
-      <c r="W1" t="str">
-        <v>championshipHistory</v>
-      </c>
-      <c r="X1" t="str">
         <v>collectorNumber</v>
       </c>
     </row>
@@ -490,74 +475,159 @@
       <c r="E2" t="str">
         <v>Monaco</v>
       </c>
-      <c r="F2" t="str">
-        <v>🇲🇨</v>
+      <c r="F2">
+        <v>1929</v>
       </c>
       <c r="G2">
-        <v>1929</v>
+        <v>37000</v>
       </c>
       <c r="H2">
-        <v>37000</v>
+        <v>43.7347</v>
       </c>
       <c r="I2">
-        <v>43.7347</v>
-      </c>
-      <c r="J2">
         <v>7.4206</v>
       </c>
+      <c r="J2" t="str">
+        <v>Charles Leclerc</v>
+      </c>
       <c r="K2" t="str">
-        <v>Charles Leclerc</v>
-      </c>
-      <c r="L2" t="str">
         <v>Asphalt</v>
       </c>
-      <c r="M2" t="str">
-        <v>#1a1a1a</v>
+      <c r="L2">
+        <v>3.337</v>
+      </c>
+      <c r="M2">
+        <v>19</v>
       </c>
       <c r="N2" t="str">
-        <v>#c41e3a</v>
+        <v>Street Circuit in the Sky</v>
       </c>
       <c r="O2" t="str">
-        <v>#d4af37</v>
+        <v>Prestige,Street circuit,Glamour</v>
       </c>
       <c r="P2" t="str">
-        <v>Street circuit,Prestige,Casino</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>Senna victory record|Leclerc home win 2024</v>
-      </c>
-      <c r="R2">
-        <v>3.337</v>
-      </c>
-      <c r="S2">
-        <v>19</v>
-      </c>
-      <c r="T2">
-        <v>65</v>
-      </c>
-      <c r="U2" t="str">
-        <v>Street Circuit in the Sky</v>
-      </c>
-      <c r="V2" t="str">
-        <v>F1 Championship|Monaco Grand Prix</v>
-      </c>
-      <c r="W2" t="str">
-        <v>Senna 6 times|Leclerc 2024</v>
-      </c>
-      <c r="X2">
+        <v>Senna victories|Leclerc home win 2024</v>
+      </c>
+      <c r="Q2">
         <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B3" t="str">
+        <v>British Grand Prix</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Silverstone Circuit</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Northamptonshire</v>
+      </c>
+      <c r="E3" t="str">
+        <v>United Kingdom</v>
+      </c>
+      <c r="F3">
+        <v>1948</v>
+      </c>
+      <c r="G3">
+        <v>140000</v>
+      </c>
+      <c r="H3">
+        <v>52.0786</v>
+      </c>
+      <c r="I3">
+        <v>-1.0169</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Historic Design</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="L3">
+        <v>5.891</v>
+      </c>
+      <c r="M3">
+        <v>18</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Home of British Racing</v>
+      </c>
+      <c r="O3" t="str">
+        <v>Speed,Racing heritage,History</v>
+      </c>
+      <c r="P3" t="str">
+        <v>First F1 race 1950|Hamilton records</v>
+      </c>
+      <c r="Q3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Italian Grand Prix</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Autodromo di Monza</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Monza</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="F4">
+        <v>1922</v>
+      </c>
+      <c r="G4">
+        <v>80000</v>
+      </c>
+      <c r="H4">
+        <v>45.6211</v>
+      </c>
+      <c r="I4">
+        <v>9.2819</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="L4">
+        <v>5.793</v>
+      </c>
+      <c r="M4">
+        <v>11</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Temple of Speed</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Speed,High speed,Tradition</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Senna-Prost crash|Schumacher wins</v>
+      </c>
+      <c r="Q4">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:X2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:O5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -576,60 +646,39 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
-        <v>countryFlag</v>
+        <v>opened</v>
       </c>
       <c r="G1" t="str">
-        <v>opened</v>
+        <v>capacity</v>
       </c>
       <c r="H1" t="str">
-        <v>capacity</v>
+        <v>lat</v>
       </c>
       <c r="I1" t="str">
-        <v>lat</v>
+        <v>lng</v>
       </c>
       <c r="J1" t="str">
-        <v>lng</v>
+        <v>architect</v>
       </c>
       <c r="K1" t="str">
-        <v>architect</v>
+        <v>surface</v>
       </c>
       <c r="L1" t="str">
-        <v>surface</v>
+        <v>nickname</v>
       </c>
       <c r="M1" t="str">
-        <v>themePrimary</v>
+        <v>famousFor</v>
       </c>
       <c r="N1" t="str">
-        <v>themeSecondary</v>
+        <v>iconicMoments</v>
       </c>
       <c r="O1" t="str">
-        <v>themeAccent</v>
-      </c>
-      <c r="P1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="R1" t="str">
-        <v>altitude</v>
-      </c>
-      <c r="S1" t="str">
-        <v>nickname</v>
-      </c>
-      <c r="T1" t="str">
-        <v>notableEvents</v>
-      </c>
-      <c r="U1" t="str">
-        <v>championshipHistory</v>
-      </c>
-      <c r="V1" t="str">
         <v>collectorNumber</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Football Stadiums</v>
+        <v>Football</v>
       </c>
       <c r="B2" t="str">
         <v>Premier League</v>
@@ -643,61 +692,952 @@
       <c r="E2" t="str">
         <v>England</v>
       </c>
-      <c r="F2" t="str">
-        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      <c r="F2">
+        <v>1910</v>
       </c>
       <c r="G2">
-        <v>1910</v>
+        <v>74310</v>
       </c>
       <c r="H2">
-        <v>74310</v>
+        <v>53.4629</v>
       </c>
       <c r="I2">
-        <v>53.4629</v>
-      </c>
-      <c r="J2">
         <v>-2.2913</v>
       </c>
+      <c r="J2" t="str">
+        <v>Archibald Leitch</v>
+      </c>
       <c r="K2" t="str">
-        <v>Archibald Leitch</v>
+        <v>Grass</v>
       </c>
       <c r="L2" t="str">
+        <v>Theatre of Dreams</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Manchester United,History,Iconic</v>
+      </c>
+      <c r="N2" t="str">
+        <v>FA Cup wins|European victories</v>
+      </c>
+      <c r="O2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B3" t="str">
+        <v>La Liga</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Camp Nou</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="F3">
+        <v>1957</v>
+      </c>
+      <c r="G3">
+        <v>99354</v>
+      </c>
+      <c r="H3">
+        <v>41.3815</v>
+      </c>
+      <c r="I3">
+        <v>2.1212</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Josep Soteras</v>
+      </c>
+      <c r="K3" t="str">
         <v>Grass</v>
       </c>
-      <c r="M2" t="str">
-        <v>#DA291C</v>
-      </c>
-      <c r="N2" t="str">
-        <v>#000000</v>
-      </c>
-      <c r="O2" t="str">
-        <v>#FDB913</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Theatre of Dreams,Rich history,Manchester United</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>First FA Cup win 1909|European dominance</v>
-      </c>
-      <c r="R2">
-        <v>34</v>
-      </c>
-      <c r="S2" t="str">
-        <v>Theatre of Dreams</v>
-      </c>
-      <c r="T2" t="str">
-        <v>Premier League|FA Cup|Champions League</v>
-      </c>
-      <c r="U2" t="str">
-        <v>Manchester United 20 titles</v>
-      </c>
-      <c r="V2">
-        <v>2</v>
+      <c r="L3" t="str">
+        <v>Camp of Wonders</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Barcelona FC,Capacity,Architecture</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Messi era|Champions League wins</v>
+      </c>
+      <c r="O3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Serie A</v>
+      </c>
+      <c r="C4" t="str">
+        <v>San Siro</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Milan</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="F4">
+        <v>1926</v>
+      </c>
+      <c r="G4">
+        <v>80018</v>
+      </c>
+      <c r="H4">
+        <v>45.4771</v>
+      </c>
+      <c r="I4">
+        <v>9.1289</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Armando Dazzi</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Stadio Giuseppe Meazza</v>
+      </c>
+      <c r="M4" t="str">
+        <v>AC Milan,Inter Milan,Derby</v>
+      </c>
+      <c r="N4" t="str">
+        <v>European Cups|Derby matches</v>
+      </c>
+      <c r="O4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Premier League</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Wembley Stadium</v>
+      </c>
+      <c r="D5" t="str">
+        <v>London</v>
+      </c>
+      <c r="E5" t="str">
+        <v>England</v>
+      </c>
+      <c r="F5">
+        <v>2019</v>
+      </c>
+      <c r="G5">
+        <v>90000</v>
+      </c>
+      <c r="H5">
+        <v>51.5559</v>
+      </c>
+      <c r="I5">
+        <v>-0.2795</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Norman Foster</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Home of Football</v>
+      </c>
+      <c r="M5" t="str">
+        <v>England home,1966 victory,Modern</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Euro 2020 final|England victories</v>
+      </c>
+      <c r="O5">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:V2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sport</v>
+      </c>
+      <c r="B1" t="str">
+        <v>competition</v>
+      </c>
+      <c r="C1" t="str">
+        <v>venueName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>city</v>
+      </c>
+      <c r="E1" t="str">
+        <v>country</v>
+      </c>
+      <c r="F1" t="str">
+        <v>opened</v>
+      </c>
+      <c r="G1" t="str">
+        <v>capacity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lng</v>
+      </c>
+      <c r="J1" t="str">
+        <v>architect</v>
+      </c>
+      <c r="K1" t="str">
+        <v>surface</v>
+      </c>
+      <c r="L1" t="str">
+        <v>nickname</v>
+      </c>
+      <c r="M1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="N1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="O1" t="str">
+        <v>collectorNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Cricket</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Test Cricket</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Lords Cricket Ground</v>
+      </c>
+      <c r="D2" t="str">
+        <v>London</v>
+      </c>
+      <c r="E2" t="str">
+        <v>England</v>
+      </c>
+      <c r="F2">
+        <v>1814</v>
+      </c>
+      <c r="G2">
+        <v>30000</v>
+      </c>
+      <c r="H2">
+        <v>51.5156</v>
+      </c>
+      <c r="I2">
+        <v>-0.1244</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Thomas Lord</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Home of Cricket</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Historic,Tradition,MCC</v>
+      </c>
+      <c r="N2" t="str">
+        <v>First match 1877|Test cricket hub</v>
+      </c>
+      <c r="O2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Cricket</v>
+      </c>
+      <c r="B3" t="str">
+        <v>IPL</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Eden Gardens</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Kolkata</v>
+      </c>
+      <c r="E3" t="str">
+        <v>India</v>
+      </c>
+      <c r="F3">
+        <v>1934</v>
+      </c>
+      <c r="G3">
+        <v>68000</v>
+      </c>
+      <c r="H3">
+        <v>22.5651</v>
+      </c>
+      <c r="I3">
+        <v>88.3828</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Historic Design</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Castle of Cricket</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Passionate crowds,Historic,India</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Test victories|IPL finals</v>
+      </c>
+      <c r="O3">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sport</v>
+      </c>
+      <c r="B1" t="str">
+        <v>competition</v>
+      </c>
+      <c r="C1" t="str">
+        <v>venueName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>city</v>
+      </c>
+      <c r="E1" t="str">
+        <v>country</v>
+      </c>
+      <c r="F1" t="str">
+        <v>opened</v>
+      </c>
+      <c r="G1" t="str">
+        <v>capacity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lng</v>
+      </c>
+      <c r="J1" t="str">
+        <v>architect</v>
+      </c>
+      <c r="K1" t="str">
+        <v>surface</v>
+      </c>
+      <c r="L1" t="str">
+        <v>nickname</v>
+      </c>
+      <c r="M1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="N1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="O1" t="str">
+        <v>collectorNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Tennis</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Wimbledon</v>
+      </c>
+      <c r="C2" t="str">
+        <v>All England Lawn Tennis Club</v>
+      </c>
+      <c r="D2" t="str">
+        <v>London</v>
+      </c>
+      <c r="E2" t="str">
+        <v>England</v>
+      </c>
+      <c r="F2">
+        <v>1877</v>
+      </c>
+      <c r="G2">
+        <v>15000</v>
+      </c>
+      <c r="H2">
+        <v>51.4347</v>
+      </c>
+      <c r="I2">
+        <v>-0.2157</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Historic Design</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Mecca of Tennis</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Grand Slam,Grass courts,Tradition</v>
+      </c>
+      <c r="N2" t="str">
+        <v>First Grand Slam 1877|Murray 2013</v>
+      </c>
+      <c r="O2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Tennis</v>
+      </c>
+      <c r="B3" t="str">
+        <v>US Open</v>
+      </c>
+      <c r="C3" t="str">
+        <v>USTA National Tennis Center</v>
+      </c>
+      <c r="D3" t="str">
+        <v>New York</v>
+      </c>
+      <c r="E3" t="str">
+        <v>USA</v>
+      </c>
+      <c r="F3">
+        <v>1978</v>
+      </c>
+      <c r="G3">
+        <v>24000</v>
+      </c>
+      <c r="H3">
+        <v>40.7589</v>
+      </c>
+      <c r="I3">
+        <v>-73.8204</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Modern Design</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Hard court</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Arthur Ashe Stadium</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Grand Slam,Hard court,American</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Serena dominance|Nadal records</v>
+      </c>
+      <c r="O3">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O3"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sport</v>
+      </c>
+      <c r="B1" t="str">
+        <v>competition</v>
+      </c>
+      <c r="C1" t="str">
+        <v>venueName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>city</v>
+      </c>
+      <c r="E1" t="str">
+        <v>country</v>
+      </c>
+      <c r="F1" t="str">
+        <v>opened</v>
+      </c>
+      <c r="G1" t="str">
+        <v>capacity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lng</v>
+      </c>
+      <c r="J1" t="str">
+        <v>architect</v>
+      </c>
+      <c r="K1" t="str">
+        <v>surface</v>
+      </c>
+      <c r="L1" t="str">
+        <v>nickname</v>
+      </c>
+      <c r="M1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="N1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="O1" t="str">
+        <v>collectorNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Golf</v>
+      </c>
+      <c r="B2" t="str">
+        <v>The Open Championship</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Old Course at St Andrews</v>
+      </c>
+      <c r="D2" t="str">
+        <v>St Andrews</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Scotland</v>
+      </c>
+      <c r="F2">
+        <v>1552</v>
+      </c>
+      <c r="G2">
+        <v>40000</v>
+      </c>
+      <c r="H2">
+        <v>56.3903</v>
+      </c>
+      <c r="I2">
+        <v>-2.7933</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Natural course</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Links grass</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Home of Golf</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Oldest course,Historic,Links</v>
+      </c>
+      <c r="N2" t="str">
+        <v>First tournament 1873|Tiger wins</v>
+      </c>
+      <c r="O2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Golf</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Masters Tournament</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Augusta National Golf Club</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Augusta</v>
+      </c>
+      <c r="E3" t="str">
+        <v>USA</v>
+      </c>
+      <c r="F3">
+        <v>1933</v>
+      </c>
+      <c r="G3">
+        <v>30000</v>
+      </c>
+      <c r="H3">
+        <v>33.5028</v>
+      </c>
+      <c r="I3">
+        <v>-82.0138</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Bobby Jones</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Championship grass</v>
+      </c>
+      <c r="L3" t="str">
+        <v>The Masters</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Green jacket,Prestige,Tradition</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Tiger comeback 2019|Nicklaus era</v>
+      </c>
+      <c r="O3">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sport</v>
+      </c>
+      <c r="B1" t="str">
+        <v>competition</v>
+      </c>
+      <c r="C1" t="str">
+        <v>venueName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>city</v>
+      </c>
+      <c r="E1" t="str">
+        <v>country</v>
+      </c>
+      <c r="F1" t="str">
+        <v>opened</v>
+      </c>
+      <c r="G1" t="str">
+        <v>capacity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lng</v>
+      </c>
+      <c r="J1" t="str">
+        <v>architect</v>
+      </c>
+      <c r="K1" t="str">
+        <v>surface</v>
+      </c>
+      <c r="L1" t="str">
+        <v>nickname</v>
+      </c>
+      <c r="M1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="N1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="O1" t="str">
+        <v>collectorNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Rugby</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Six Nations</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Twickenham Stadium</v>
+      </c>
+      <c r="D2" t="str">
+        <v>London</v>
+      </c>
+      <c r="E2" t="str">
+        <v>England</v>
+      </c>
+      <c r="F2">
+        <v>1907</v>
+      </c>
+      <c r="G2">
+        <v>82000</v>
+      </c>
+      <c r="H2">
+        <v>51.4545</v>
+      </c>
+      <c r="I2">
+        <v>-0.3394</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Archibald Leitch</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Fortress England</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Rugby HQ,Historic,England home</v>
+      </c>
+      <c r="N2" t="str">
+        <v>1999 World Cup|England Grand Slams</v>
+      </c>
+      <c r="O2">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sport</v>
+      </c>
+      <c r="B1" t="str">
+        <v>competition</v>
+      </c>
+      <c r="C1" t="str">
+        <v>venueName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>city</v>
+      </c>
+      <c r="E1" t="str">
+        <v>country</v>
+      </c>
+      <c r="F1" t="str">
+        <v>opened</v>
+      </c>
+      <c r="G1" t="str">
+        <v>capacity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lng</v>
+      </c>
+      <c r="J1" t="str">
+        <v>architect</v>
+      </c>
+      <c r="K1" t="str">
+        <v>surface</v>
+      </c>
+      <c r="L1" t="str">
+        <v>nickname</v>
+      </c>
+      <c r="M1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="N1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="O1" t="str">
+        <v>collectorNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Olympic Venues</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Summer Olympics</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Estadio Nacional de Beijing</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Beijing</v>
+      </c>
+      <c r="E2" t="str">
+        <v>China</v>
+      </c>
+      <c r="F2">
+        <v>2008</v>
+      </c>
+      <c r="G2">
+        <v>91000</v>
+      </c>
+      <c r="H2">
+        <v>39.9942</v>
+      </c>
+      <c r="I2">
+        <v>116.4074</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Herzog and de Meuron</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Track and field</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Bird's Nest</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Architecture,Beijing 2008,Modern</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Bolt records|Phelps 8 golds</v>
+      </c>
+      <c r="O2">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O2"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>sport</v>
+      </c>
+      <c r="B1" t="str">
+        <v>competition</v>
+      </c>
+      <c r="C1" t="str">
+        <v>venueName</v>
+      </c>
+      <c r="D1" t="str">
+        <v>city</v>
+      </c>
+      <c r="E1" t="str">
+        <v>country</v>
+      </c>
+      <c r="F1" t="str">
+        <v>opened</v>
+      </c>
+      <c r="G1" t="str">
+        <v>capacity</v>
+      </c>
+      <c r="H1" t="str">
+        <v>lat</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lng</v>
+      </c>
+      <c r="J1" t="str">
+        <v>architect</v>
+      </c>
+      <c r="K1" t="str">
+        <v>surface</v>
+      </c>
+      <c r="L1" t="str">
+        <v>nickname</v>
+      </c>
+      <c r="M1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="N1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="O1" t="str">
+        <v>collectorNumber</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Boxing</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Title Fights</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Madison Square Garden</v>
+      </c>
+      <c r="D2" t="str">
+        <v>New York</v>
+      </c>
+      <c r="E2" t="str">
+        <v>USA</v>
+      </c>
+      <c r="F2">
+        <v>1968</v>
+      </c>
+      <c r="G2">
+        <v>20000</v>
+      </c>
+      <c r="H2">
+        <v>40.7505</v>
+      </c>
+      <c r="I2">
+        <v>-73.9934</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Modern Design</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Indoor arena</v>
+      </c>
+      <c r="L2" t="str">
+        <v>The Garden</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Boxing history,Title fights,Iconic</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Ali vs Frazier 1971|Tyson fights</v>
+      </c>
+      <c r="O2">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/databases/iconic-venues.xlsx
+++ b/public/databases/iconic-venues.xlsx
@@ -404,7 +404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:AA24"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,39 +423,69 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>venueMap</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="P1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="R1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="S1" t="str">
+        <v>dimensions</v>
+      </c>
+      <c r="T1" t="str">
         <v>raceDistance</v>
       </c>
-      <c r="M1" t="str">
+      <c r="U1" t="str">
         <v>numberOfTurns</v>
       </c>
-      <c r="N1" t="str">
+      <c r="V1" t="str">
+        <v>altitude</v>
+      </c>
+      <c r="W1" t="str">
+        <v>historicRecords</v>
+      </c>
+      <c r="X1" t="str">
         <v>nickname</v>
       </c>
-      <c r="O1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="P1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="Q1" t="str">
+      <c r="Y1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="AA1" t="str">
         <v>collectorNumber</v>
       </c>
     </row>
@@ -475,40 +505,70 @@
       <c r="E2" t="str">
         <v>Monaco</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>🇲🇨</v>
+      </c>
+      <c r="G2">
         <v>1929</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>37000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>43.7347</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>7.4206</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Charles Leclerc</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Asphalt</v>
       </c>
-      <c r="L2">
+      <c r="M2" t="str">
+        <v>Street layout</v>
+      </c>
+      <c r="N2" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#c41e3a</v>
+      </c>
+      <c r="P2" t="str">
+        <v>#d4af37</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Prestige,Street circuit,Glamour</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Senna victories|Leclerc home</v>
+      </c>
+      <c r="S2" t="str">
+        <v>2.074km</v>
+      </c>
+      <c r="T2">
         <v>3.337</v>
       </c>
-      <c r="M2">
+      <c r="U2">
         <v>19</v>
       </c>
-      <c r="N2" t="str">
-        <v>Street Circuit in the Sky</v>
-      </c>
-      <c r="O2" t="str">
-        <v>Prestige,Street circuit,Glamour</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Senna victories|Leclerc home win 2024</v>
-      </c>
-      <c r="Q2">
+      <c r="V2">
+        <v>65</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Senna 6 wins</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Circuit in the Sky</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Grand Pomp</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Senna legend</v>
+      </c>
+      <c r="AA2">
         <v>1</v>
       </c>
     </row>
@@ -528,40 +588,70 @@
       <c r="E3" t="str">
         <v>United Kingdom</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
+        <v>🇬🇧</v>
+      </c>
+      <c r="G3">
         <v>1948</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>140000</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>52.0786</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>-1.0169</v>
       </c>
-      <c r="J3" t="str">
-        <v>Historic Design</v>
-      </c>
       <c r="K3" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L3" t="str">
         <v>Asphalt</v>
       </c>
-      <c r="L3">
+      <c r="M3" t="str">
+        <v>High-speed</v>
+      </c>
+      <c r="N3" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#012169</v>
+      </c>
+      <c r="P3" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Speed,Heritage,First F1</v>
+      </c>
+      <c r="R3" t="str">
+        <v>First F1 race</v>
+      </c>
+      <c r="S3" t="str">
+        <v>High-speed</v>
+      </c>
+      <c r="T3">
         <v>5.891</v>
       </c>
-      <c r="M3">
+      <c r="U3">
         <v>18</v>
       </c>
-      <c r="N3" t="str">
+      <c r="V3">
+        <v>56</v>
+      </c>
+      <c r="W3" t="str">
+        <v>First F1 ever</v>
+      </c>
+      <c r="X3" t="str">
         <v>Home of British Racing</v>
       </c>
-      <c r="O3" t="str">
-        <v>Speed,Racing heritage,History</v>
-      </c>
-      <c r="P3" t="str">
-        <v>First F1 race 1950|Hamilton records</v>
-      </c>
-      <c r="Q3">
+      <c r="Y3" t="str">
+        <v>British tradition</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>British legacy</v>
+      </c>
+      <c r="AA3">
         <v>2</v>
       </c>
     </row>
@@ -581,53 +671,1743 @@
       <c r="E4" t="str">
         <v>Italy</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
+        <v>🇮🇹</v>
+      </c>
+      <c r="G4">
         <v>1922</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>80000</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>45.6211</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>9.2819</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>Historic</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>Asphalt</v>
       </c>
-      <c r="L4">
+      <c r="M4" t="str">
+        <v>Figure-eight</v>
+      </c>
+      <c r="N4" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#009246</v>
+      </c>
+      <c r="P4" t="str">
+        <v>#D4AF37</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Speed,Tradition,Racing</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Senna-Prost crash</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Figure-eight</v>
+      </c>
+      <c r="T4">
         <v>5.793</v>
       </c>
-      <c r="M4">
+      <c r="U4">
         <v>11</v>
       </c>
-      <c r="N4" t="str">
+      <c r="V4">
+        <v>102</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Speed records</v>
+      </c>
+      <c r="X4" t="str">
         <v>Temple of Speed</v>
       </c>
-      <c r="O4" t="str">
-        <v>Speed,High speed,Tradition</v>
-      </c>
-      <c r="P4" t="str">
-        <v>Senna-Prost crash|Schumacher wins</v>
-      </c>
-      <c r="Q4">
+      <c r="Y4" t="str">
+        <v>Italian Grand Prix</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>F1 tradition</v>
+      </c>
+      <c r="AA4">
         <v>3</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Spanish Grand Prix</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Circuit de Barcelona-Catalunya</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Barcelona</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="F5" t="str">
+        <v>🇪🇸</v>
+      </c>
+      <c r="G5">
+        <v>1991</v>
+      </c>
+      <c r="H5">
+        <v>109000</v>
+      </c>
+      <c r="I5">
+        <v>41.5699</v>
+      </c>
+      <c r="J5">
+        <v>2.2614</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFC400</v>
+      </c>
+      <c r="P5" t="str">
+        <v>#D4AF37</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Technical,Testing,Modern</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Spring development</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="T5">
+        <v>4.655</v>
+      </c>
+      <c r="U5">
+        <v>16</v>
+      </c>
+      <c r="V5">
+        <v>14</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Testing ground</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Technical Circuit</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Development venue</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>Modern F1</v>
+      </c>
+      <c r="AA5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>German Grand Prix</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Nürburgring</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Nürburg</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="F6" t="str">
+        <v>🇩🇪</v>
+      </c>
+      <c r="G6">
+        <v>1927</v>
+      </c>
+      <c r="H6">
+        <v>150000</v>
+      </c>
+      <c r="I6">
+        <v>50.3387</v>
+      </c>
+      <c r="J6">
+        <v>6.9473</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Challenging</v>
+      </c>
+      <c r="N6" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O6" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="P6" t="str">
+        <v>#D4AF37</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Challenging,History,Tradition</v>
+      </c>
+      <c r="R6" t="str">
+        <v>Schumacher era</v>
+      </c>
+      <c r="S6" t="str">
+        <v>Challenging</v>
+      </c>
+      <c r="T6">
+        <v>5.148</v>
+      </c>
+      <c r="U6">
+        <v>15</v>
+      </c>
+      <c r="V6">
+        <v>320</v>
+      </c>
+      <c r="W6" t="str">
+        <v>Schumacher records</v>
+      </c>
+      <c r="X6" t="str">
+        <v>Green Hell</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>German tradition</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>Historic venue</v>
+      </c>
+      <c r="AA6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B7" t="str">
+        <v>French Grand Prix</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Circuit Paul Ricard</v>
+      </c>
+      <c r="D7" t="str">
+        <v>Le Castellet</v>
+      </c>
+      <c r="E7" t="str">
+        <v>France</v>
+      </c>
+      <c r="F7" t="str">
+        <v>🇫🇷</v>
+      </c>
+      <c r="G7">
+        <v>1970</v>
+      </c>
+      <c r="H7">
+        <v>90000</v>
+      </c>
+      <c r="I7">
+        <v>43.2505</v>
+      </c>
+      <c r="J7">
+        <v>5.7917</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="N7" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O7" t="str">
+        <v>#002395</v>
+      </c>
+      <c r="P7" t="str">
+        <v>#D4AF37</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>Testing,Modern,Technical</v>
+      </c>
+      <c r="R7" t="str">
+        <v>Testing improvements</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="T7">
+        <v>5.842</v>
+      </c>
+      <c r="U7">
+        <v>15</v>
+      </c>
+      <c r="V7">
+        <v>220</v>
+      </c>
+      <c r="W7" t="str">
+        <v>Testing facility</v>
+      </c>
+      <c r="X7" t="str">
+        <v>French Riviera</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>French motorsport</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>Modern facility</v>
+      </c>
+      <c r="AA7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Austrian Grand Prix</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Red Bull Ring</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Spielberg</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Austria</v>
+      </c>
+      <c r="F8" t="str">
+        <v>🇦🇹</v>
+      </c>
+      <c r="G8">
+        <v>1969</v>
+      </c>
+      <c r="H8">
+        <v>70000</v>
+      </c>
+      <c r="I8">
+        <v>47.2136</v>
+      </c>
+      <c r="J8">
+        <v>14.7619</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Alpine</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Alpine</v>
+      </c>
+      <c r="N8" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O8" t="str">
+        <v>#002395</v>
+      </c>
+      <c r="P8" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>High-speed,Alpine,Vettel</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Vettel victories</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Alpine</v>
+      </c>
+      <c r="T8">
+        <v>4.318</v>
+      </c>
+      <c r="U8">
+        <v>10</v>
+      </c>
+      <c r="V8">
+        <v>640</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Short lap</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Alpine Circuit</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>Red Bull home</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>Vettel legacy</v>
+      </c>
+      <c r="AA8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Hungarian Grand Prix</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Hungaroring</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Budapest</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Hungary</v>
+      </c>
+      <c r="F9" t="str">
+        <v>🇭🇺</v>
+      </c>
+      <c r="G9">
+        <v>1986</v>
+      </c>
+      <c r="H9">
+        <v>80000</v>
+      </c>
+      <c r="I9">
+        <v>47.5811</v>
+      </c>
+      <c r="J9">
+        <v>19.2479</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Tight</v>
+      </c>
+      <c r="N9" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O9" t="str">
+        <v>#CE2B37</v>
+      </c>
+      <c r="P9" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>Technical,Tight,Racing</v>
+      </c>
+      <c r="R9" t="str">
+        <v>Close racing</v>
+      </c>
+      <c r="S9" t="str">
+        <v>Tight</v>
+      </c>
+      <c r="T9">
+        <v>4.381</v>
+      </c>
+      <c r="U9">
+        <v>14</v>
+      </c>
+      <c r="V9">
+        <v>185</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Technical mastery</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Budapest Circuit</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>Hungarian pride</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>Eastern Europe</v>
+      </c>
+      <c r="AA9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Belgian Grand Prix</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Circuit de Spa-Francorchamps</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Spa</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Belgium</v>
+      </c>
+      <c r="F10" t="str">
+        <v>🇧🇪</v>
+      </c>
+      <c r="G10">
+        <v>1925</v>
+      </c>
+      <c r="H10">
+        <v>140000</v>
+      </c>
+      <c r="I10">
+        <v>50.4372</v>
+      </c>
+      <c r="J10">
+        <v>5.9708</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M10" t="str">
+        <v>High-speed</v>
+      </c>
+      <c r="N10" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O10" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P10" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Speed,Rain,Tradition</v>
+      </c>
+      <c r="R10" t="str">
+        <v>Senna crashes</v>
+      </c>
+      <c r="S10" t="str">
+        <v>7km</v>
+      </c>
+      <c r="T10">
+        <v>7.004</v>
+      </c>
+      <c r="U10">
+        <v>19</v>
+      </c>
+      <c r="V10">
+        <v>380</v>
+      </c>
+      <c r="W10" t="str">
+        <v>Rain records</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Wet Track</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>Belgian tradition</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="AA10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Dutch Grand Prix</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Circuit Zandvoort</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Zandvoort</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Netherlands</v>
+      </c>
+      <c r="F11" t="str">
+        <v>🇳🇱</v>
+      </c>
+      <c r="G11">
+        <v>1948</v>
+      </c>
+      <c r="H11">
+        <v>70000</v>
+      </c>
+      <c r="I11">
+        <v>52.3083</v>
+      </c>
+      <c r="J11">
+        <v>4.5406</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Coastal</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M11" t="str">
+        <v>Banked</v>
+      </c>
+      <c r="N11" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O11" t="str">
+        <v>#FF6600</v>
+      </c>
+      <c r="P11" t="str">
+        <v>#0066CC</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>Banking,Coastal,Verstappen</v>
+      </c>
+      <c r="R11" t="str">
+        <v>Verstappen home</v>
+      </c>
+      <c r="S11" t="str">
+        <v>Banked</v>
+      </c>
+      <c r="T11">
+        <v>4.259</v>
+      </c>
+      <c r="U11">
+        <v>14</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11" t="str">
+        <v>Verstappen records</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Beach Circuit</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>Dutch return</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>Dutch pride</v>
+      </c>
+      <c r="AA11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Singapore Grand Prix</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Marina Bay Street Circuit</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Singapore</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Singapore</v>
+      </c>
+      <c r="F12" t="str">
+        <v>🇸🇬</v>
+      </c>
+      <c r="G12">
+        <v>2008</v>
+      </c>
+      <c r="H12">
+        <v>60000</v>
+      </c>
+      <c r="I12">
+        <v>1.2947</v>
+      </c>
+      <c r="J12">
+        <v>103.8627</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Urban</v>
+      </c>
+      <c r="L12" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Street</v>
+      </c>
+      <c r="N12" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O12" t="str">
+        <v>#C8102E</v>
+      </c>
+      <c r="P12" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>Night,Street,Urban</v>
+      </c>
+      <c r="R12" t="str">
+        <v>First night race</v>
+      </c>
+      <c r="S12" t="str">
+        <v>Street</v>
+      </c>
+      <c r="T12">
+        <v>5.065</v>
+      </c>
+      <c r="U12">
+        <v>23</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12" t="str">
+        <v>Night racing</v>
+      </c>
+      <c r="X12" t="str">
+        <v>Night Race</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>Singapore tradition</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>Night innovation</v>
+      </c>
+      <c r="AA12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Japanese Grand Prix</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Suzuka International Racing Course</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Suzuka</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Japan</v>
+      </c>
+      <c r="F13" t="str">
+        <v>🇯🇵</v>
+      </c>
+      <c r="G13">
+        <v>1962</v>
+      </c>
+      <c r="H13">
+        <v>155000</v>
+      </c>
+      <c r="I13">
+        <v>34.8434</v>
+      </c>
+      <c r="J13">
+        <v>136.5425</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Figure-Eight</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Figure-eight</v>
+      </c>
+      <c r="N13" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O13" t="str">
+        <v>#BC002D</v>
+      </c>
+      <c r="P13" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>Unique,Senna,Tradition</v>
+      </c>
+      <c r="R13" t="str">
+        <v>Senna-Prost crashes</v>
+      </c>
+      <c r="S13" t="str">
+        <v>Figure-eight</v>
+      </c>
+      <c r="T13">
+        <v>5.807</v>
+      </c>
+      <c r="U13">
+        <v>18</v>
+      </c>
+      <c r="V13">
+        <v>45</v>
+      </c>
+      <c r="W13" t="str">
+        <v>Senna-Prost history</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Figure Eight</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>Japanese motorsport</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>Japanese legacy</v>
+      </c>
+      <c r="AA13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Brazilian Grand Prix</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Autódromo José Carlos Pace</v>
+      </c>
+      <c r="D14" t="str">
+        <v>São Paulo</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Brazil</v>
+      </c>
+      <c r="F14" t="str">
+        <v>🇧🇷</v>
+      </c>
+      <c r="G14">
+        <v>1940</v>
+      </c>
+      <c r="H14">
+        <v>98000</v>
+      </c>
+      <c r="I14">
+        <v>-23.2176</v>
+      </c>
+      <c r="J14">
+        <v>-46.5608</v>
+      </c>
+      <c r="K14" t="str">
+        <v>South American</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Challenging</v>
+      </c>
+      <c r="N14" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O14" t="str">
+        <v>#009C3B</v>
+      </c>
+      <c r="P14" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>Passion,Rain,Senna</v>
+      </c>
+      <c r="R14" t="str">
+        <v>Senna triumphs</v>
+      </c>
+      <c r="S14" t="str">
+        <v>Challenging</v>
+      </c>
+      <c r="T14">
+        <v>4.309</v>
+      </c>
+      <c r="U14">
+        <v>15</v>
+      </c>
+      <c r="V14">
+        <v>800</v>
+      </c>
+      <c r="W14" t="str">
+        <v>Rain epic</v>
+      </c>
+      <c r="X14" t="str">
+        <v>Interlagos</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>Brazilian hub</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>Brazilian legend</v>
+      </c>
+      <c r="AA14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Abu Dhabi Grand Prix</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Yas Marina Circuit</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Abu Dhabi</v>
+      </c>
+      <c r="E15" t="str">
+        <v>United Arab Emirates</v>
+      </c>
+      <c r="F15" t="str">
+        <v>🇦🇪</v>
+      </c>
+      <c r="G15">
+        <v>2009</v>
+      </c>
+      <c r="H15">
+        <v>65000</v>
+      </c>
+      <c r="I15">
+        <v>24.467</v>
+      </c>
+      <c r="J15">
+        <v>54.353</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Desert</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="N15" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O15" t="str">
+        <v>#CE1126</v>
+      </c>
+      <c r="P15" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Modern,Season-finale,Night</v>
+      </c>
+      <c r="R15" t="str">
+        <v>Championship deciders</v>
+      </c>
+      <c r="S15" t="str">
+        <v>Desert</v>
+      </c>
+      <c r="T15">
+        <v>5.281</v>
+      </c>
+      <c r="U15">
+        <v>21</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15" t="str">
+        <v>Season finale</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Desert Circuit</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>Finale tradition</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>Modern Middle East</v>
+      </c>
+      <c r="AA15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Australian Grand Prix</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Albert Park Circuit</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="F16" t="str">
+        <v>🇦🇺</v>
+      </c>
+      <c r="G16">
+        <v>1953</v>
+      </c>
+      <c r="H16">
+        <v>110000</v>
+      </c>
+      <c r="I16">
+        <v>-37.8477</v>
+      </c>
+      <c r="J16">
+        <v>144.9679</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Street</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Street</v>
+      </c>
+      <c r="N16" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O16" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P16" t="str">
+        <v>#00843D</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>Opener,Street,Season-start</v>
+      </c>
+      <c r="R16" t="str">
+        <v>Season starts</v>
+      </c>
+      <c r="S16" t="str">
+        <v>Street</v>
+      </c>
+      <c r="T16">
+        <v>5.278</v>
+      </c>
+      <c r="U16">
+        <v>16</v>
+      </c>
+      <c r="V16">
+        <v>10</v>
+      </c>
+      <c r="W16" t="str">
+        <v>Opener</v>
+      </c>
+      <c r="X16" t="str">
+        <v>Australian Grand Prix</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>Season beginning</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>Southern hemisphere</v>
+      </c>
+      <c r="AA16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Canadian Grand Prix</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Circuit Gilles Villeneuve</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Montreal</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Canada</v>
+      </c>
+      <c r="F17" t="str">
+        <v>🇨🇦</v>
+      </c>
+      <c r="G17">
+        <v>1978</v>
+      </c>
+      <c r="H17">
+        <v>105000</v>
+      </c>
+      <c r="I17">
+        <v>45.5017</v>
+      </c>
+      <c r="J17">
+        <v>-73.5246</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Island</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Street</v>
+      </c>
+      <c r="N17" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O17" t="str">
+        <v>#C8102E</v>
+      </c>
+      <c r="P17" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>Street,Villeneuve,North America</v>
+      </c>
+      <c r="R17" t="str">
+        <v>Villeneuve tribute</v>
+      </c>
+      <c r="S17" t="str">
+        <v>Street</v>
+      </c>
+      <c r="T17">
+        <v>4.361</v>
+      </c>
+      <c r="U17">
+        <v>14</v>
+      </c>
+      <c r="V17">
+        <v>10</v>
+      </c>
+      <c r="W17" t="str">
+        <v>Villeneuve memory</v>
+      </c>
+      <c r="X17" t="str">
+        <v>Gilles Villeneuve</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>Canadian Grand Prix</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>North American</v>
+      </c>
+      <c r="AA17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B18" t="str">
+        <v>US Grand Prix</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Circuit of The Americas</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Austin</v>
+      </c>
+      <c r="E18" t="str">
+        <v>United States</v>
+      </c>
+      <c r="F18" t="str">
+        <v>🇺🇸</v>
+      </c>
+      <c r="G18">
+        <v>2012</v>
+      </c>
+      <c r="H18">
+        <v>120000</v>
+      </c>
+      <c r="I18">
+        <v>30.1325</v>
+      </c>
+      <c r="J18">
+        <v>-97.6411</v>
+      </c>
+      <c r="K18" t="str">
+        <v>American</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Hill-based</v>
+      </c>
+      <c r="N18" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O18" t="str">
+        <v>#002868</v>
+      </c>
+      <c r="P18" t="str">
+        <v>#BF0A30</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>Modern,American,Texas</v>
+      </c>
+      <c r="R18" t="str">
+        <v>F1 renaissance</v>
+      </c>
+      <c r="S18" t="str">
+        <v>Hill-based</v>
+      </c>
+      <c r="T18">
+        <v>5.513</v>
+      </c>
+      <c r="U18">
+        <v>20</v>
+      </c>
+      <c r="V18">
+        <v>220</v>
+      </c>
+      <c r="W18" t="str">
+        <v>Modern American</v>
+      </c>
+      <c r="X18" t="str">
+        <v>American Circuit</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>US return</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>F1 USA</v>
+      </c>
+      <c r="AA18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Mexican Grand Prix</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Autodromo Hermanos Rodríguez</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Mexico City</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Mexico</v>
+      </c>
+      <c r="F19" t="str">
+        <v>🇲🇽</v>
+      </c>
+      <c r="G19">
+        <v>1962</v>
+      </c>
+      <c r="H19">
+        <v>137000</v>
+      </c>
+      <c r="I19">
+        <v>19.4042</v>
+      </c>
+      <c r="J19">
+        <v>-99.0904</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Altitude</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Altitude</v>
+      </c>
+      <c r="N19" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O19" t="str">
+        <v>#CE1126</v>
+      </c>
+      <c r="P19" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Altitude,Mexican,Thin-air</v>
+      </c>
+      <c r="R19" t="str">
+        <v>Mexican drivers</v>
+      </c>
+      <c r="S19" t="str">
+        <v>Altitude</v>
+      </c>
+      <c r="T19">
+        <v>4.304</v>
+      </c>
+      <c r="U19">
+        <v>17</v>
+      </c>
+      <c r="V19">
+        <v>2250</v>
+      </c>
+      <c r="W19" t="str">
+        <v>Highest F1</v>
+      </c>
+      <c r="X19" t="str">
+        <v>Altitude Circuit</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>Mexican motorsport</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>Mexico tradition</v>
+      </c>
+      <c r="AA19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Saudi Arabian Grand Prix</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Jeddah Corniche Circuit</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Jeddah</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Saudi Arabia</v>
+      </c>
+      <c r="F20" t="str">
+        <v>🇸🇦</v>
+      </c>
+      <c r="G20">
+        <v>2021</v>
+      </c>
+      <c r="H20">
+        <v>62000</v>
+      </c>
+      <c r="I20">
+        <v>21.5433</v>
+      </c>
+      <c r="J20">
+        <v>39.1054</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Street</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Coastal-street</v>
+      </c>
+      <c r="N20" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O20" t="str">
+        <v>#006C35</v>
+      </c>
+      <c r="P20" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>High-speed,Street,Modern</v>
+      </c>
+      <c r="R20" t="str">
+        <v>Speed records</v>
+      </c>
+      <c r="S20" t="str">
+        <v>Street</v>
+      </c>
+      <c r="T20">
+        <v>6.174</v>
+      </c>
+      <c r="U20">
+        <v>27</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20" t="str">
+        <v>Fastest street</v>
+      </c>
+      <c r="X20" t="str">
+        <v>Fastest Street</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>Saudi debut</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>Modern Middle East</v>
+      </c>
+      <c r="AA20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Chinese Grand Prix</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Shanghai International Circuit</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Shanghai</v>
+      </c>
+      <c r="E21" t="str">
+        <v>China</v>
+      </c>
+      <c r="F21" t="str">
+        <v>🇨🇳</v>
+      </c>
+      <c r="G21">
+        <v>2004</v>
+      </c>
+      <c r="H21">
+        <v>200000</v>
+      </c>
+      <c r="I21">
+        <v>31.3393</v>
+      </c>
+      <c r="J21">
+        <v>121.205</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Shanghai</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="N21" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O21" t="str">
+        <v>#DE2910</v>
+      </c>
+      <c r="P21" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Modern,Asian,Capacity</v>
+      </c>
+      <c r="R21" t="str">
+        <v>Asian expansion</v>
+      </c>
+      <c r="S21" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="T21">
+        <v>5.451</v>
+      </c>
+      <c r="U21">
+        <v>16</v>
+      </c>
+      <c r="V21">
+        <v>5</v>
+      </c>
+      <c r="W21" t="str">
+        <v>Largest capacity</v>
+      </c>
+      <c r="X21" t="str">
+        <v>Chinese Grand Prix</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>Asian Formula 1</v>
+      </c>
+      <c r="Z21" t="str">
+        <v>Asian expansion</v>
+      </c>
+      <c r="AA21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Thai Grand Prix</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Chang International Circuit</v>
+      </c>
+      <c r="D22" t="str">
+        <v>Buriram</v>
+      </c>
+      <c r="E22" t="str">
+        <v>Thailand</v>
+      </c>
+      <c r="F22" t="str">
+        <v>🇹🇭</v>
+      </c>
+      <c r="G22">
+        <v>2018</v>
+      </c>
+      <c r="H22">
+        <v>50000</v>
+      </c>
+      <c r="I22">
+        <v>14.5419</v>
+      </c>
+      <c r="J22">
+        <v>103.2386</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Southeast-Asian</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="N22" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O22" t="str">
+        <v>#CE1126</v>
+      </c>
+      <c r="P22" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>Southeast-Asia,Modern,Chang</v>
+      </c>
+      <c r="R22" t="str">
+        <v>Asian expansion</v>
+      </c>
+      <c r="S22" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="T22">
+        <v>4.655</v>
+      </c>
+      <c r="U22">
+        <v>12</v>
+      </c>
+      <c r="V22">
+        <v>45</v>
+      </c>
+      <c r="W22" t="str">
+        <v>Thailand debut</v>
+      </c>
+      <c r="X22" t="str">
+        <v>Thai Circuit</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>Thailand motorsport</v>
+      </c>
+      <c r="Z22" t="str">
+        <v>Southeast Asia</v>
+      </c>
+      <c r="AA22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B23" t="str">
+        <v>Las Vegas Grand Prix</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Las Vegas Street Circuit</v>
+      </c>
+      <c r="D23" t="str">
+        <v>Las Vegas</v>
+      </c>
+      <c r="E23" t="str">
+        <v>United States</v>
+      </c>
+      <c r="F23" t="str">
+        <v>🇺🇸</v>
+      </c>
+      <c r="G23">
+        <v>2023</v>
+      </c>
+      <c r="H23">
+        <v>18000</v>
+      </c>
+      <c r="I23">
+        <v>36.1699</v>
+      </c>
+      <c r="J23">
+        <v>-115.1398</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Street</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Strip</v>
+      </c>
+      <c r="N23" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O23" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="P23" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>Night,Vegas,Entertainment</v>
+      </c>
+      <c r="R23" t="str">
+        <v>Newest venue</v>
+      </c>
+      <c r="S23" t="str">
+        <v>Street</v>
+      </c>
+      <c r="T23">
+        <v>6.12</v>
+      </c>
+      <c r="U23">
+        <v>17</v>
+      </c>
+      <c r="V23">
+        <v>600</v>
+      </c>
+      <c r="W23" t="str">
+        <v>Newest F1</v>
+      </c>
+      <c r="X23" t="str">
+        <v>Vegas Grand Prix</v>
+      </c>
+      <c r="Y23" t="str">
+        <v>Vegas debut</v>
+      </c>
+      <c r="Z23" t="str">
+        <v>Entertainment</v>
+      </c>
+      <c r="AA23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>Formula 1</v>
+      </c>
+      <c r="B24" t="str">
+        <v>Qatar Grand Prix</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Lusail International Circuit</v>
+      </c>
+      <c r="D24" t="str">
+        <v>Lusail</v>
+      </c>
+      <c r="E24" t="str">
+        <v>Qatar</v>
+      </c>
+      <c r="F24" t="str">
+        <v>🇶🇦</v>
+      </c>
+      <c r="G24">
+        <v>2021</v>
+      </c>
+      <c r="H24">
+        <v>86000</v>
+      </c>
+      <c r="I24">
+        <v>25.193</v>
+      </c>
+      <c r="J24">
+        <v>51.4529</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Middle-East</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Asphalt</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="N24" t="str">
+        <v>#1a1a1a</v>
+      </c>
+      <c r="O24" t="str">
+        <v>#8B1538</v>
+      </c>
+      <c r="P24" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>Modern,Middle-East,Capacity</v>
+      </c>
+      <c r="R24" t="str">
+        <v>Qatar debut</v>
+      </c>
+      <c r="S24" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="T24">
+        <v>5.419</v>
+      </c>
+      <c r="U24">
+        <v>16</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24" t="str">
+        <v>Qatar venue</v>
+      </c>
+      <c r="X24" t="str">
+        <v>Lusail Circuit</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>Qatar motorsport</v>
+      </c>
+      <c r="Z24" t="str">
+        <v>Middle East</v>
+      </c>
+      <c r="AA24">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Q4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA24"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:AK21"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -646,34 +2426,100 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="P1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="R1" t="str">
         <v>nickname</v>
       </c>
-      <c r="M1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="T1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="U1" t="str">
+        <v>clubLogo</v>
+      </c>
+      <c r="V1" t="str">
         <v>collectorNumber</v>
+      </c>
+      <c r="W1" t="str">
+        <v>pitchDimensions</v>
+      </c>
+      <c r="X1" t="str">
+        <v>roofType</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>recordAttendance</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>europeanTitles</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>domesticTitles</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>rivalClub</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>legendaryManager</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>legendaryPlayer</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>clubRecordScorer</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>floodlightsInstalled</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>lastRenovation</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>safeStandingSection</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>groundOwnership</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>stadiumTours</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>ticketPriceRange</v>
       </c>
     </row>
     <row r="2">
@@ -692,35 +2538,101 @@
       <c r="E2" t="str">
         <v>England</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G2">
         <v>1910</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>74310</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>53.4629</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-2.2913</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Archibald Leitch</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Grass</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
+        <v>#DA291C</v>
+      </c>
+      <c r="N2" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#FDB913</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Manchester United,Historic,Theatre of Dreams</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Munich air disaster memorial|1999 Treble run</v>
+      </c>
+      <c r="R2" t="str">
         <v>Theatre of Dreams</v>
       </c>
-      <c r="M2" t="str">
-        <v>Manchester United,History,Iconic</v>
-      </c>
-      <c r="N2" t="str">
-        <v>FA Cup wins|European victories</v>
-      </c>
-      <c r="O2">
-        <v>4</v>
+      <c r="S2" t="str">
+        <v>Hosted Euro 96 semi-final</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Manchester United 20 league titles</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Manchester United</v>
+      </c>
+      <c r="V2">
+        <v>24</v>
+      </c>
+      <c r="W2" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Partial (open corners)</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>76,962 (1939 vs Wolves)</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>3 European Cups/UCL (1968, 1999, 2008)</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>20 league titles</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Manchester City / Liverpool</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Sir Alex Ferguson</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>George Best &amp; Bobby Charlton</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>Wayne Rooney (253 goals)</v>
+      </c>
+      <c r="AF2">
+        <v>1957</v>
+      </c>
+      <c r="AG2">
+        <v>2006</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>Yes (Sir Bobby Charlton Stand, 2022)</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK2" t="str">
+        <v>£35-£80</v>
       </c>
     </row>
     <row r="3">
@@ -739,35 +2651,101 @@
       <c r="E3" t="str">
         <v>Spain</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
+        <v>🇪🇸</v>
+      </c>
+      <c r="G3">
         <v>1957</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>99354</v>
       </c>
-      <c r="H3">
+      <c r="I3">
         <v>41.3815</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>2.1212</v>
       </c>
-      <c r="J3" t="str">
+      <c r="K3" t="str">
         <v>Josep Soteras</v>
       </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
         <v>Grass</v>
       </c>
-      <c r="L3" t="str">
-        <v>Camp of Wonders</v>
-      </c>
       <c r="M3" t="str">
-        <v>Barcelona FC,Capacity,Architecture</v>
+        <v>#004B9A</v>
       </c>
       <c r="N3" t="str">
-        <v>Messi era|Champions League wins</v>
-      </c>
-      <c r="O3">
-        <v>5</v>
+        <v>#DC143C</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#FFC500</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Barcelona FC,Largest stadium in Europe,Messi era</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Messi 672-goal era|1992 European Cup Final host</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Camp Nou</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Undergoing Espai Barça redevelopment</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Barcelona 27 La Liga titles</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Barcelona FC</v>
+      </c>
+      <c r="V3">
+        <v>25</v>
+      </c>
+      <c r="W3" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>121,000 (1986 vs Juventus)</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>5 European Cups/UCL</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>27 La Liga titles</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Real Madrid (El Clásico)</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>Johan Cruyff &amp; Pep Guardiola</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>Lionel Messi</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Lionel Messi (672 goals)</v>
+      </c>
+      <c r="AF3">
+        <v>1957</v>
+      </c>
+      <c r="AG3">
+        <v>2024</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK3" t="str">
+        <v>€60-€150</v>
       </c>
     </row>
     <row r="4">
@@ -786,35 +2764,101 @@
       <c r="E4" t="str">
         <v>Italy</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
+        <v>🇮🇹</v>
+      </c>
+      <c r="G4">
         <v>1926</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <v>80018</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <v>45.4771</v>
       </c>
-      <c r="I4">
+      <c r="J4">
         <v>9.1289</v>
       </c>
-      <c r="J4" t="str">
+      <c r="K4" t="str">
         <v>Armando Dazzi</v>
       </c>
-      <c r="K4" t="str">
+      <c r="L4" t="str">
         <v>Grass</v>
       </c>
-      <c r="L4" t="str">
-        <v>Stadio Giuseppe Meazza</v>
-      </c>
       <c r="M4" t="str">
-        <v>AC Milan,Inter Milan,Derby</v>
+        <v>#000000</v>
       </c>
       <c r="N4" t="str">
-        <v>European Cups|Derby matches</v>
-      </c>
-      <c r="O4">
-        <v>6</v>
+        <v>#FF0000</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P4" t="str">
+        <v>AC Milan,Inter Milan,Derby della Madonnina</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Shared home of two European giants|Derby della Madonnina</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Meazza</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Hosted 2016 Champions League Final</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Milan + Inter 39 combined Serie A titles</v>
+      </c>
+      <c r="U4" t="str">
+        <v>AC Milan | Inter Milan</v>
+      </c>
+      <c r="V4">
+        <v>26</v>
+      </c>
+      <c r="W4" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>82,955 (1985 Milan derby)</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>AC Milan 7 + Inter 3 European Cups/UCL</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>39 combined Serie A titles</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>Derby della Madonnina (shared ground)</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>Arrigo Sacchi (Milan) / Helenio Herrera (Inter)</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>Paolo Maldini &amp; Javier Zanetti</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>N/A — shared ground, two clubs</v>
+      </c>
+      <c r="AF4">
+        <v>1959</v>
+      </c>
+      <c r="AG4">
+        <v>2016</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>City of Milan (shared)</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>Yes (San Siro Museum)</v>
+      </c>
+      <c r="AK4" t="str">
+        <v>€40-€120</v>
       </c>
     </row>
     <row r="5">
@@ -825,55 +2869,1929 @@
         <v>Premier League</v>
       </c>
       <c r="C5" t="str">
-        <v>Wembley Stadium</v>
+        <v>Anfield</v>
       </c>
       <c r="D5" t="str">
-        <v>London</v>
+        <v>Liverpool</v>
       </c>
       <c r="E5" t="str">
         <v>England</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G5">
+        <v>1892</v>
+      </c>
+      <c r="H5">
+        <v>61276</v>
+      </c>
+      <c r="I5">
+        <v>53.4309</v>
+      </c>
+      <c r="J5">
+        <v>-2.9609</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M5" t="str">
+        <v>#C8102E</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#FFF8DC</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Liverpool FC,The Kop,You’ll Never Walk Alone</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>2005 Champions League "Miracle of Istanbul" comeback</v>
+      </c>
+      <c r="R5" t="str">
+        <v>The Fortress</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Home of "You’ll Never Walk Alone" anthem</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Liverpool 19 league titles</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Liverpool FC</v>
+      </c>
+      <c r="V5">
+        <v>27</v>
+      </c>
+      <c r="W5" t="str">
+        <v>101m x 68m</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Partial (Main Stand roof)</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>61,905 (1952 vs Wolves)</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>6 European Cups/UCL</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>19 league titles</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>Everton (Merseyside Derby)</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>Bill Shankly</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>Steven Gerrard</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>Ian Rush (346 goals)</v>
+      </c>
+      <c r="AF5">
+        <v>1957</v>
+      </c>
+      <c r="AG5">
+        <v>2023</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>Yes (Kop &amp; Anfield Road, 2023)</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK5" t="str">
+        <v>£45-£75</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Bundesliga</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Allianz Arena</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Munich</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="F6" t="str">
+        <v>🇩🇪</v>
+      </c>
+      <c r="G6">
+        <v>2006</v>
+      </c>
+      <c r="H6">
+        <v>75024</v>
+      </c>
+      <c r="I6">
+        <v>48.2189</v>
+      </c>
+      <c r="J6">
+        <v>11.6241</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Herzog &amp; de Meuron</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M6" t="str">
+        <v>#FF0000</v>
+      </c>
+      <c r="N6" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O6" t="str">
+        <v>#000080</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Bayern Munich,Illuminated ETFE facade,Modern icon</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Colour-changing facade unveiled 2006 World Cup</v>
+      </c>
+      <c r="R6" t="str">
+        <v>Red Arena</v>
+      </c>
+      <c r="S6" t="str">
+        <v>Hosted 2012 Champions League Final</v>
+      </c>
+      <c r="T6" t="str">
+        <v>Bayern Munich 33 Bundesliga titles</v>
+      </c>
+      <c r="U6" t="str">
+        <v>Bayern Munich</v>
+      </c>
+      <c r="V6">
+        <v>28</v>
+      </c>
+      <c r="W6" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X6" t="str">
+        <v>Fully covered, illuminated ETFE facade</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>75,024 (regular sellouts)</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>6 European Cups/UCL</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>33 Bundesliga titles</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>Borussia Dortmund (Der Klassiker)</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>Pep Guardiola &amp; Jupp Heynckes</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>Franz Beckenbauer</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>Gerd Müller (566 goals)</v>
+      </c>
+      <c r="AF6">
+        <v>2005</v>
+      </c>
+      <c r="AG6">
+        <v>2005</v>
+      </c>
+      <c r="AH6" t="str">
+        <v>Yes (visitor section)</v>
+      </c>
+      <c r="AI6" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK6" t="str">
+        <v>€35-€90</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Premier League</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Stamford Bridge</v>
+      </c>
+      <c r="D7" t="str">
+        <v>London</v>
+      </c>
+      <c r="E7" t="str">
+        <v>England</v>
+      </c>
+      <c r="F7" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G7">
+        <v>1905</v>
+      </c>
+      <c r="H7">
+        <v>60450</v>
+      </c>
+      <c r="I7">
+        <v>51.482</v>
+      </c>
+      <c r="J7">
+        <v>-0.1914</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L7" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M7" t="str">
+        <v>#0055B8</v>
+      </c>
+      <c r="N7" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O7" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Chelsea FC,West London,Modern-era powerhouse</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>2012 &amp; 2021 Champions League titles won under Chelsea era</v>
+      </c>
+      <c r="R7" t="str">
+        <v>The Bridge</v>
+      </c>
+      <c r="S7" t="str">
+        <v>Original home of the FA Charity Shield (1920)</v>
+      </c>
+      <c r="T7" t="str">
+        <v>Chelsea 6 league titles</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Chelsea FC</v>
+      </c>
+      <c r="V7">
+        <v>29</v>
+      </c>
+      <c r="W7" t="str">
+        <v>103m x 67m</v>
+      </c>
+      <c r="X7" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>82,905 (1935 vs Arsenal)</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>2 UEFA Champions League (2012, 2021)</v>
+      </c>
+      <c r="AA7" t="str">
+        <v>6 league titles</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>Tottenham Hotspur / Arsenal</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>José Mourinho</v>
+      </c>
+      <c r="AD7" t="str">
+        <v>Frank Lampard</v>
+      </c>
+      <c r="AE7" t="str">
+        <v>Frank Lampard (211 goals)</v>
+      </c>
+      <c r="AF7">
+        <v>1957</v>
+      </c>
+      <c r="AG7">
+        <v>2001</v>
+      </c>
+      <c r="AH7" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI7" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK7" t="str">
+        <v>£60-£100</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Premier League</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Etihad Stadium</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Manchester</v>
+      </c>
+      <c r="E8" t="str">
+        <v>England</v>
+      </c>
+      <c r="F8" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G8">
+        <v>2002</v>
+      </c>
+      <c r="H8">
+        <v>61776</v>
+      </c>
+      <c r="I8">
+        <v>53.4829</v>
+      </c>
+      <c r="J8">
+        <v>-2.2004</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="L8" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M8" t="str">
+        <v>#6CABDA</v>
+      </c>
+      <c r="N8" t="str">
+        <v>#FDB913</v>
+      </c>
+      <c r="O8" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="P8" t="str">
+        <v>Manchester City,Built for 2002 Commonwealth Games,Modern dominance</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>2023 Treble-winning season</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Etihad</v>
+      </c>
+      <c r="S8" t="str">
+        <v>Originally built as 2002 Commonwealth Games athletics stadium</v>
+      </c>
+      <c r="T8" t="str">
+        <v>Manchester City 10 league titles</v>
+      </c>
+      <c r="U8" t="str">
+        <v>Manchester City</v>
+      </c>
+      <c r="V8">
+        <v>30</v>
+      </c>
+      <c r="W8" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X8" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>54,693 (post-conversion record)</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>1 UEFA Champions League (2023)</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>10 league titles</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>Manchester United</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>Pep Guardiola</v>
+      </c>
+      <c r="AD8" t="str">
+        <v>Sergio Agüero</v>
+      </c>
+      <c r="AE8" t="str">
+        <v>Sergio Agüero (260 goals)</v>
+      </c>
+      <c r="AF8">
+        <v>2003</v>
+      </c>
+      <c r="AG8">
+        <v>2015</v>
+      </c>
+      <c r="AH8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AI8" t="str">
+        <v>Club-owned (formerly city council)</v>
+      </c>
+      <c r="AJ8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK8" t="str">
+        <v>£45-£85</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B9" t="str">
+        <v>La Liga</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Santiago Bernabéu</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="F9" t="str">
+        <v>🇪🇸</v>
+      </c>
+      <c r="G9">
+        <v>1947</v>
+      </c>
+      <c r="H9">
+        <v>81044</v>
+      </c>
+      <c r="I9">
+        <v>40.453</v>
+      </c>
+      <c r="J9">
+        <v>-3.6883</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L9" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M9" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="N9" t="str">
+        <v>#333333</v>
+      </c>
+      <c r="O9" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Real Madrid,Record 15 European Cups,Recently rebuilt</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>1956-60 five consecutive European Cups</v>
+      </c>
+      <c r="R9" t="str">
+        <v>Bernabéu</v>
+      </c>
+      <c r="S9" t="str">
+        <v>Reopened 2024 after full retractable-roof rebuild</v>
+      </c>
+      <c r="T9" t="str">
+        <v>Real Madrid 36 La Liga titles</v>
+      </c>
+      <c r="U9" t="str">
+        <v>Real Madrid</v>
+      </c>
+      <c r="V9">
+        <v>31</v>
+      </c>
+      <c r="W9" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X9" t="str">
+        <v>Fully retractable (2024 rebuild)</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>129,690 (1956 European Cup)</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>15 European Cups/UCL (record)</v>
+      </c>
+      <c r="AA9" t="str">
+        <v>36 La Liga titles</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>Barcelona (El Clásico) / Atlético Madrid</v>
+      </c>
+      <c r="AC9" t="str">
+        <v>Miguel Muñoz &amp; Zinedine Zidane</v>
+      </c>
+      <c r="AD9" t="str">
+        <v>Alfredo Di Stéfano &amp; Cristiano Ronaldo</v>
+      </c>
+      <c r="AE9" t="str">
+        <v>Cristiano Ronaldo (450 goals)</v>
+      </c>
+      <c r="AF9">
+        <v>1957</v>
+      </c>
+      <c r="AG9">
+        <v>2024</v>
+      </c>
+      <c r="AH9" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI9" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK9" t="str">
+        <v>€60-€150</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Ligue 1</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Parc des Princes</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E10" t="str">
+        <v>France</v>
+      </c>
+      <c r="F10" t="str">
+        <v>🇫🇷</v>
+      </c>
+      <c r="G10">
+        <v>1897</v>
+      </c>
+      <c r="H10">
+        <v>47929</v>
+      </c>
+      <c r="I10">
+        <v>48.8449</v>
+      </c>
+      <c r="J10">
+        <v>2.2534</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L10" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M10" t="str">
+        <v>#004B87</v>
+      </c>
+      <c r="N10" t="str">
+        <v>#F7931E</v>
+      </c>
+      <c r="O10" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="P10" t="str">
+        <v>Paris Saint-Germain,Third stadium on the site since 1897,Modern era power</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>Mbappé and Messi era arrivals</v>
+      </c>
+      <c r="R10" t="str">
+        <v>Prince Park</v>
+      </c>
+      <c r="S10" t="str">
+        <v>Also used for Tour de France finish historically</v>
+      </c>
+      <c r="T10" t="str">
+        <v>PSG 12 Ligue 1 titles</v>
+      </c>
+      <c r="U10" t="str">
+        <v>PSG</v>
+      </c>
+      <c r="V10">
+        <v>32</v>
+      </c>
+      <c r="W10" t="str">
+        <v>103m x 68m</v>
+      </c>
+      <c r="X10" t="str">
+        <v>Fully covered</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>49,575</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>0 (UCL runner-up 2020)</v>
+      </c>
+      <c r="AA10" t="str">
+        <v>12 Ligue 1 titles</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>Olympique Marseille (Le Classique)</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>Luis Fernández</v>
+      </c>
+      <c r="AD10" t="str">
+        <v>Kylian Mbappé</v>
+      </c>
+      <c r="AE10" t="str">
+        <v>Kylian Mbappé (256 goals)</v>
+      </c>
+      <c r="AF10">
+        <v>1972</v>
+      </c>
+      <c r="AG10">
+        <v>2011</v>
+      </c>
+      <c r="AH10" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI10" t="str">
+        <v>City of Paris (leased to PSG)</v>
+      </c>
+      <c r="AJ10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK10" t="str">
+        <v>€40-€120</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Série A</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Estádio do Maracanã</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Rio de Janeiro</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Brazil</v>
+      </c>
+      <c r="F11" t="str">
+        <v>🇧🇷</v>
+      </c>
+      <c r="G11">
+        <v>1950</v>
+      </c>
+      <c r="H11">
+        <v>78838</v>
+      </c>
+      <c r="I11">
+        <v>-22.9068</v>
+      </c>
+      <c r="J11">
+        <v>-43.2322</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Oscar Niemeyer (renovation)</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M11" t="str">
+        <v>#009639</v>
+      </c>
+      <c r="N11" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="O11" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="P11" t="str">
+        <v>1950 World Cup Final,Rio de Janeiro icon,Fla-Flu derby</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>1950 World Cup Final "Maracanazo"</v>
+      </c>
+      <c r="R11" t="str">
+        <v>Maracanã</v>
+      </c>
+      <c r="S11" t="str">
+        <v>Hosted 2014 World Cup Final &amp; 2016 Olympics ceremonies</v>
+      </c>
+      <c r="T11" t="str">
+        <v>Home to Flamengo &amp; Fluminense</v>
+      </c>
+      <c r="U11" t="str">
+        <v>Brazil National Team</v>
+      </c>
+      <c r="V11">
+        <v>33</v>
+      </c>
+      <c r="W11" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X11" t="str">
+        <v>Partial ring roof</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>~199,854 (1950 World Cup Final)</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>Flamengo most Rio state titles</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>Flamengo vs Fluminense (Fla-Flu)</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>N/A — national/multi-club stadium</v>
+      </c>
+      <c r="AD11" t="str">
+        <v>Pelé (scored his 1,000th career goal here, 1969)</v>
+      </c>
+      <c r="AE11" t="str">
+        <v>Zico (Flamengo)</v>
+      </c>
+      <c r="AF11">
+        <v>1950</v>
+      </c>
+      <c r="AG11">
+        <v>2013</v>
+      </c>
+      <c r="AH11" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI11" t="str">
+        <v>State of Rio de Janeiro</v>
+      </c>
+      <c r="AJ11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK11" t="str">
+        <v>R$60-R$300</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Premier League</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Tottenham Hotspur Stadium</v>
+      </c>
+      <c r="D12" t="str">
+        <v>London</v>
+      </c>
+      <c r="E12" t="str">
+        <v>England</v>
+      </c>
+      <c r="F12" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G12">
         <v>2019</v>
       </c>
-      <c r="G5">
-        <v>90000</v>
-      </c>
-      <c r="H5">
-        <v>51.5559</v>
-      </c>
-      <c r="I5">
-        <v>-0.2795</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Norman Foster</v>
-      </c>
-      <c r="K5" t="str">
+      <c r="H12">
+        <v>62850</v>
+      </c>
+      <c r="I12">
+        <v>51.6039</v>
+      </c>
+      <c r="J12">
+        <v>-0.0657</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Populous</v>
+      </c>
+      <c r="L12" t="str">
         <v>Grass</v>
       </c>
-      <c r="L5" t="str">
-        <v>Home of Football</v>
-      </c>
-      <c r="M5" t="str">
-        <v>England home,1966 victory,Modern</v>
-      </c>
-      <c r="N5" t="str">
-        <v>Euro 2020 final|England victories</v>
-      </c>
-      <c r="O5">
-        <v>7</v>
+      <c r="M12" t="str">
+        <v>#132257</v>
+      </c>
+      <c r="N12" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O12" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P12" t="str">
+        <v>Tottenham Hotspur,Dual NFL/football pitch,Largest club stand in UK</v>
+      </c>
+      <c r="Q12" t="str">
+        <v>First stadium with a dividing retractable NFL pitch</v>
+      </c>
+      <c r="R12" t="str">
+        <v>New White Hart Lane</v>
+      </c>
+      <c r="S12" t="str">
+        <v>Regular NFL London Games host</v>
+      </c>
+      <c r="T12" t="str">
+        <v>Tottenham 2 English top-flight titles (pre-PL era)</v>
+      </c>
+      <c r="U12" t="str">
+        <v>Tottenham Hotspur</v>
+      </c>
+      <c r="V12">
+        <v>47</v>
+      </c>
+      <c r="W12" t="str">
+        <v>105m x 68m (dividing NFL pitch beneath)</v>
+      </c>
+      <c r="X12" t="str">
+        <v>Retractable dual-pitch system</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>62,850 (sold out)</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>2 UEFA Cup/Europa League</v>
+      </c>
+      <c r="AA12" t="str">
+        <v>2 English top-flight titles</v>
+      </c>
+      <c r="AB12" t="str">
+        <v>Arsenal (North London Derby)</v>
+      </c>
+      <c r="AC12" t="str">
+        <v>Bill Nicholson</v>
+      </c>
+      <c r="AD12" t="str">
+        <v>Harry Kane</v>
+      </c>
+      <c r="AE12" t="str">
+        <v>Harry Kane (280 goals)</v>
+      </c>
+      <c r="AF12">
+        <v>2019</v>
+      </c>
+      <c r="AG12">
+        <v>2019</v>
+      </c>
+      <c r="AH12" t="str">
+        <v>Yes (South Stand, 17,500 — largest single-tier stand in UK)</v>
+      </c>
+      <c r="AI12" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ12" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK12" t="str">
+        <v>£40-£95</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Premier League</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Emirates Stadium</v>
+      </c>
+      <c r="D13" t="str">
+        <v>London</v>
+      </c>
+      <c r="E13" t="str">
+        <v>England</v>
+      </c>
+      <c r="F13" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G13">
+        <v>2006</v>
+      </c>
+      <c r="H13">
+        <v>60704</v>
+      </c>
+      <c r="I13">
+        <v>51.5549</v>
+      </c>
+      <c r="J13">
+        <v>-0.1084</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Populous</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M13" t="str">
+        <v>#EF0107</v>
+      </c>
+      <c r="N13" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O13" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P13" t="str">
+        <v>Arsenal,Replaced Highbury in 2006,North London</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>Invincibles legacy carried over from Highbury (2003-04)</v>
+      </c>
+      <c r="R13" t="str">
+        <v>The Emirates</v>
+      </c>
+      <c r="S13" t="str">
+        <v>Hosted NFL London Games</v>
+      </c>
+      <c r="T13" t="str">
+        <v>Arsenal 13 league titles (incl. Highbury era)</v>
+      </c>
+      <c r="U13" t="str">
+        <v>Arsenal</v>
+      </c>
+      <c r="V13">
+        <v>48</v>
+      </c>
+      <c r="W13" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>60,161</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>0 (UCL runner-up 2006)</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>13 league titles</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>Tottenham Hotspur (North London Derby)</v>
+      </c>
+      <c r="AC13" t="str">
+        <v>Arsène Wenger</v>
+      </c>
+      <c r="AD13" t="str">
+        <v>Thierry Henry</v>
+      </c>
+      <c r="AE13" t="str">
+        <v>Thierry Henry (228 goals)</v>
+      </c>
+      <c r="AF13">
+        <v>2006</v>
+      </c>
+      <c r="AG13">
+        <v>2006</v>
+      </c>
+      <c r="AH13" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI13" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ13" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK13" t="str">
+        <v>£40-£95</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Premier League</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Brighton and Hove Albion Stadium</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Brighton</v>
+      </c>
+      <c r="E14" t="str">
+        <v>England</v>
+      </c>
+      <c r="F14" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G14">
+        <v>2011</v>
+      </c>
+      <c r="H14">
+        <v>31707</v>
+      </c>
+      <c r="I14">
+        <v>50.8629</v>
+      </c>
+      <c r="J14">
+        <v>-0.0835</v>
+      </c>
+      <c r="K14" t="str">
+        <v>KSS Group</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M14" t="str">
+        <v>#0054A6</v>
+      </c>
+      <c r="N14" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O14" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P14" t="str">
+        <v>Brighton &amp; Hove Albion,Coastal setting,Modern rise</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>First Europa League qualification (2023)</v>
+      </c>
+      <c r="R14" t="str">
+        <v>Amex Stadium</v>
+      </c>
+      <c r="S14" t="str">
+        <v>Replaced Withdean Stadium in 2011</v>
+      </c>
+      <c r="T14" t="str">
+        <v>No major domestic honours yet</v>
+      </c>
+      <c r="U14" t="str">
+        <v>Brighton &amp; Hove Albion</v>
+      </c>
+      <c r="V14">
+        <v>49</v>
+      </c>
+      <c r="W14" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X14" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>31,876</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA14" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB14" t="str">
+        <v>Crystal Palace (M23 Derby)</v>
+      </c>
+      <c r="AC14" t="str">
+        <v>Graham Potter</v>
+      </c>
+      <c r="AD14" t="str">
+        <v>Glenn Murray</v>
+      </c>
+      <c r="AE14" t="str">
+        <v>Glenn Murray</v>
+      </c>
+      <c r="AF14">
+        <v>2011</v>
+      </c>
+      <c r="AG14">
+        <v>2011</v>
+      </c>
+      <c r="AH14" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AI14" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ14" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK14" t="str">
+        <v>£30-£55</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Premier League</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Everton Football Club - Goodison Park</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Liverpool</v>
+      </c>
+      <c r="E15" t="str">
+        <v>England</v>
+      </c>
+      <c r="F15" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G15">
+        <v>1892</v>
+      </c>
+      <c r="H15">
+        <v>39414</v>
+      </c>
+      <c r="I15">
+        <v>53.4387</v>
+      </c>
+      <c r="J15">
+        <v>-2.6647</v>
+      </c>
+      <c r="K15" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M15" t="str">
+        <v>#003DA5</v>
+      </c>
+      <c r="N15" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O15" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P15" t="str">
+        <v>Everton FC,First purpose-built English top-flight ground,Dixie Dean legacy</v>
+      </c>
+      <c r="Q15" t="str">
+        <v>Dixie Dean’s record 60 league goals in a season (1927-28)</v>
+      </c>
+      <c r="R15" t="str">
+        <v>The Grand Old Lady</v>
+      </c>
+      <c r="S15" t="str">
+        <v>Club relocating to Bramley-Moore Dock (2025)</v>
+      </c>
+      <c r="T15" t="str">
+        <v>Everton 9 league titles</v>
+      </c>
+      <c r="U15" t="str">
+        <v>Everton FC</v>
+      </c>
+      <c r="V15">
+        <v>50</v>
+      </c>
+      <c r="W15" t="str">
+        <v>100.5m x 68m</v>
+      </c>
+      <c r="X15" t="str">
+        <v>Partial (historic stands)</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>78,299 (1938 vs Liverpool)</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>1 UEFA Cup Winners’ Cup (1985)</v>
+      </c>
+      <c r="AA15" t="str">
+        <v>9 league titles</v>
+      </c>
+      <c r="AB15" t="str">
+        <v>Liverpool (Merseyside Derby)</v>
+      </c>
+      <c r="AC15" t="str">
+        <v>Howard Kendall</v>
+      </c>
+      <c r="AD15" t="str">
+        <v>Dixie Dean</v>
+      </c>
+      <c r="AE15" t="str">
+        <v>Dixie Dean (383 goals)</v>
+      </c>
+      <c r="AF15">
+        <v>1957</v>
+      </c>
+      <c r="AG15">
+        <v>1994</v>
+      </c>
+      <c r="AH15" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI15" t="str">
+        <v>Club-owned (relocating 2025)</v>
+      </c>
+      <c r="AJ15" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK15" t="str">
+        <v>£30-£50</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B16" t="str">
+        <v>La Liga</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Atlético Madrid - Metropolitano</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Madrid</v>
+      </c>
+      <c r="E16" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="F16" t="str">
+        <v>🇪🇸</v>
+      </c>
+      <c r="G16">
+        <v>2017</v>
+      </c>
+      <c r="H16">
+        <v>68456</v>
+      </c>
+      <c r="I16">
+        <v>40.4354</v>
+      </c>
+      <c r="J16">
+        <v>-3.5992</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Cruz y Ortiz</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M16" t="str">
+        <v>#FF0000</v>
+      </c>
+      <c r="N16" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O16" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P16" t="str">
+        <v>Atlético Madrid,Three-time UCL runner-up,Modern rebuild of 1994 athletics stadium</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>Hosted 2019 Champions League Final</v>
+      </c>
+      <c r="R16" t="str">
+        <v>Metropolitano</v>
+      </c>
+      <c r="S16" t="str">
+        <v>Originally built as 1994 World Athletics Championships venue</v>
+      </c>
+      <c r="T16" t="str">
+        <v>Atlético 11 La Liga titles</v>
+      </c>
+      <c r="U16" t="str">
+        <v>Atlético Madrid</v>
+      </c>
+      <c r="V16">
+        <v>51</v>
+      </c>
+      <c r="W16" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X16" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>68,456</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>0 (UCL runner-up 3 times)</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>11 La Liga titles</v>
+      </c>
+      <c r="AB16" t="str">
+        <v>Real Madrid (Madrid Derby)</v>
+      </c>
+      <c r="AC16" t="str">
+        <v>Diego Simeone</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>Fernando Torres</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>Luis Aragonés</v>
+      </c>
+      <c r="AF16">
+        <v>2017</v>
+      </c>
+      <c r="AG16">
+        <v>2019</v>
+      </c>
+      <c r="AH16" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI16" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ16" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK16" t="str">
+        <v>€35-€90</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B17" t="str">
+        <v>La Liga</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Valencia CF Stadium</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Valencia</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Spain</v>
+      </c>
+      <c r="F17" t="str">
+        <v>🇪🇸</v>
+      </c>
+      <c r="G17">
+        <v>2000</v>
+      </c>
+      <c r="H17">
+        <v>55000</v>
+      </c>
+      <c r="I17">
+        <v>39.4863</v>
+      </c>
+      <c r="J17">
+        <v>-0.4317</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M17" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="N17" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="O17" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P17" t="str">
+        <v>Valencia CF,Two-time UEFA Cup winners,Historic Mestalla ground</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>Back-to-back Champions League finals (2000, 2001)</v>
+      </c>
+      <c r="R17" t="str">
+        <v>Mestalla</v>
+      </c>
+      <c r="S17" t="str">
+        <v>One of Spain’s oldest continuously used grounds</v>
+      </c>
+      <c r="T17" t="str">
+        <v>Valencia 6 La Liga titles</v>
+      </c>
+      <c r="U17" t="str">
+        <v>Valencia CF</v>
+      </c>
+      <c r="V17">
+        <v>52</v>
+      </c>
+      <c r="W17" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X17" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>73,000 (historic peak)</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>2 UEFA Cups</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>6 La Liga titles</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>Levante (Valencia Derby)</v>
+      </c>
+      <c r="AC17" t="str">
+        <v>Rafael Benítez</v>
+      </c>
+      <c r="AD17" t="str">
+        <v>David Villa</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>Mundo (historic club record)</v>
+      </c>
+      <c r="AF17">
+        <v>1959</v>
+      </c>
+      <c r="AG17">
+        <v>2001</v>
+      </c>
+      <c r="AH17" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ17" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK17" t="str">
+        <v>€25-€70</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Serie A</v>
+      </c>
+      <c r="C18" t="str">
+        <v>AS Roma - Stadio Olimpico</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Rome</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="F18" t="str">
+        <v>🇮🇹</v>
+      </c>
+      <c r="G18">
+        <v>1953</v>
+      </c>
+      <c r="H18">
+        <v>70698</v>
+      </c>
+      <c r="I18">
+        <v>41.9349</v>
+      </c>
+      <c r="J18">
+        <v>12.4555</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M18" t="str">
+        <v>#C60C30</v>
+      </c>
+      <c r="N18" t="str">
+        <v>#FDB913</v>
+      </c>
+      <c r="O18" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P18" t="str">
+        <v>AS Roma,Shared with Lazio,Athletics track surrounds pitch</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>Hosted 1990 World Cup Final &amp; 2020 Euro opener</v>
+      </c>
+      <c r="R18" t="str">
+        <v>Olimpico</v>
+      </c>
+      <c r="S18" t="str">
+        <v>Home of the Derby della Capitale</v>
+      </c>
+      <c r="T18" t="str">
+        <v>Roma 3 Serie A titles</v>
+      </c>
+      <c r="U18" t="str">
+        <v>AS Roma | SS Lazio</v>
+      </c>
+      <c r="V18">
+        <v>53</v>
+      </c>
+      <c r="W18" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X18" t="str">
+        <v>Partial (athletics track surrounds pitch)</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>82,000+</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>0 (UCL runner-up 1984)</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>3 Serie A titles (Roma)</v>
+      </c>
+      <c r="AB18" t="str">
+        <v>Lazio (Derby della Capitale, shared ground)</v>
+      </c>
+      <c r="AC18" t="str">
+        <v>Fabio Capello</v>
+      </c>
+      <c r="AD18" t="str">
+        <v>Francesco Totti</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>Francesco Totti (307 goals)</v>
+      </c>
+      <c r="AF18">
+        <v>1990</v>
+      </c>
+      <c r="AG18">
+        <v>1990</v>
+      </c>
+      <c r="AH18" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI18" t="str">
+        <v>CONI (Italian Olympic Committee)</v>
+      </c>
+      <c r="AJ18" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK18" t="str">
+        <v>€30-€90</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Serie A</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Napoli - San Paolo</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Naples</v>
+      </c>
+      <c r="E19" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="F19" t="str">
+        <v>🇮🇹</v>
+      </c>
+      <c r="G19">
+        <v>1959</v>
+      </c>
+      <c r="H19">
+        <v>50598</v>
+      </c>
+      <c r="I19">
+        <v>40.8259</v>
+      </c>
+      <c r="J19">
+        <v>14.2267</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M19" t="str">
+        <v>#66CCFF</v>
+      </c>
+      <c r="N19" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O19" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P19" t="str">
+        <v>Napoli,Renamed for Diego Maradona in 2020,2023 Scudetto</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>Maradona’s two Scudetti (1987, 1990)</v>
+      </c>
+      <c r="R19" t="str">
+        <v>Stadio Diego Armando Maradona</v>
+      </c>
+      <c r="S19" t="str">
+        <v>Renamed days after Maradona’s death (Dec 2020)</v>
+      </c>
+      <c r="T19" t="str">
+        <v>Napoli 3 Serie A titles</v>
+      </c>
+      <c r="U19" t="str">
+        <v>Napoli</v>
+      </c>
+      <c r="V19">
+        <v>54</v>
+      </c>
+      <c r="W19" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X19" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>90,000+ (1970s peak, since reduced)</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>0 (UEFA Cup winners 1989)</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>3 Serie A titles (2 with Maradona, 1 in 2023)</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>Juventus (rivalry of South vs North)</v>
+      </c>
+      <c r="AC19" t="str">
+        <v>Luciano Spalletti</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>Diego Maradona</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>Marek Hamsik</v>
+      </c>
+      <c r="AF19">
+        <v>1990</v>
+      </c>
+      <c r="AG19">
+        <v>1990</v>
+      </c>
+      <c r="AH19" t="str">
+        <v>No</v>
+      </c>
+      <c r="AI19" t="str">
+        <v>City of Naples</v>
+      </c>
+      <c r="AJ19" t="str">
+        <v>Yes (Maradona Museum)</v>
+      </c>
+      <c r="AK19" t="str">
+        <v>€25-€80</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Bundesliga</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Borussia Dortmund - Signal Iduna Park</v>
+      </c>
+      <c r="D20" t="str">
+        <v>Dortmund</v>
+      </c>
+      <c r="E20" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="F20" t="str">
+        <v>🇩🇪</v>
+      </c>
+      <c r="G20">
+        <v>1974</v>
+      </c>
+      <c r="H20">
+        <v>81365</v>
+      </c>
+      <c r="I20">
+        <v>51.4434</v>
+      </c>
+      <c r="J20">
+        <v>7.4653</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M20" t="str">
+        <v>#FFED00</v>
+      </c>
+      <c r="N20" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="O20" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Borussia Dortmund,The Yellow Wall,Largest standing terrace in Europe</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>1997 Champions League title|2013 Wembley UCL final run</v>
+      </c>
+      <c r="R20" t="str">
+        <v>Signal Iduna Park</v>
+      </c>
+      <c r="S20" t="str">
+        <v>Home of the "Yellow Wall" (Südtribüne)</v>
+      </c>
+      <c r="T20" t="str">
+        <v>Dortmund 8 Bundesliga titles</v>
+      </c>
+      <c r="U20" t="str">
+        <v>Borussia Dortmund</v>
+      </c>
+      <c r="V20">
+        <v>55</v>
+      </c>
+      <c r="W20" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X20" t="str">
+        <v>Partial</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>83,100 (Bundesliga attendance record)</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>1 UEFA Champions League (1997)</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>8 Bundesliga titles</v>
+      </c>
+      <c r="AB20" t="str">
+        <v>Schalke 04 (Revierderby)</v>
+      </c>
+      <c r="AC20" t="str">
+        <v>Jürgen Klopp</v>
+      </c>
+      <c r="AD20" t="str">
+        <v>Marco Reus</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>Michael Zorc (159 Bundesliga goals)</v>
+      </c>
+      <c r="AF20">
+        <v>1974</v>
+      </c>
+      <c r="AG20">
+        <v>2003</v>
+      </c>
+      <c r="AH20" t="str">
+        <v>Yes (Südtribüne "Yellow Wall", ~24,454 standing capacity)</v>
+      </c>
+      <c r="AI20" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ20" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK20" t="str">
+        <v>€20-€65</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Football</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Bundesliga</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Schalke 04 - Veltins-Arena</v>
+      </c>
+      <c r="D21" t="str">
+        <v>Gelsenkirchen</v>
+      </c>
+      <c r="E21" t="str">
+        <v>Germany</v>
+      </c>
+      <c r="F21" t="str">
+        <v>🇩🇪</v>
+      </c>
+      <c r="G21">
+        <v>2001</v>
+      </c>
+      <c r="H21">
+        <v>62271</v>
+      </c>
+      <c r="I21">
+        <v>51.4552</v>
+      </c>
+      <c r="J21">
+        <v>7.0845</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M21" t="str">
+        <v>#004B95</v>
+      </c>
+      <c r="N21" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O21" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P21" t="str">
+        <v>Schalke 04,Fully retractable roof &amp; sliding pitch,Ruhr valley heritage</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>One of the first stadiums with a sliding outdoor pitch tray</v>
+      </c>
+      <c r="R21" t="str">
+        <v>Veltins-Arena</v>
+      </c>
+      <c r="S21" t="str">
+        <v>Hosted 2004 Champions League Final</v>
+      </c>
+      <c r="T21" t="str">
+        <v>Schalke 7 German titles (mostly pre-Bundesliga era)</v>
+      </c>
+      <c r="U21" t="str">
+        <v>Schalke 04</v>
+      </c>
+      <c r="V21">
+        <v>56</v>
+      </c>
+      <c r="W21" t="str">
+        <v>105m x 68m</v>
+      </c>
+      <c r="X21" t="str">
+        <v>Fully retractable + sliding pitch tray</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>61,673</v>
+      </c>
+      <c r="Z21" t="str">
+        <v>0 (UEFA Cup runner-up 1997)</v>
+      </c>
+      <c r="AA21" t="str">
+        <v>7 German titles (mostly pre-Bundesliga era)</v>
+      </c>
+      <c r="AB21" t="str">
+        <v>Borussia Dortmund (Revierderby)</v>
+      </c>
+      <c r="AC21" t="str">
+        <v>Rudi Assauer (executive/manager)</v>
+      </c>
+      <c r="AD21" t="str">
+        <v>Klaus Fischer</v>
+      </c>
+      <c r="AE21" t="str">
+        <v>Klaus Fischer</v>
+      </c>
+      <c r="AF21">
+        <v>2001</v>
+      </c>
+      <c r="AG21">
+        <v>2001</v>
+      </c>
+      <c r="AH21" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AI21" t="str">
+        <v>Club-owned</v>
+      </c>
+      <c r="AJ21" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AK21" t="str">
+        <v>€25-€60</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AK21"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:AI6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -892,34 +4810,94 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="P1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="R1" t="str">
         <v>nickname</v>
       </c>
-      <c r="M1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="T1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="U1" t="str">
         <v>collectorNumber</v>
+      </c>
+      <c r="V1" t="str">
+        <v>groundType</v>
+      </c>
+      <c r="W1" t="str">
+        <v>endsNames</v>
+      </c>
+      <c r="X1" t="str">
+        <v>highestTestScore</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>mostTestsHosted</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>famousFeature</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>pitchType</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>dayNightCapable</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>firstTestYear</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>domesticTeamResident</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>worldCupFinalsHosted</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>boundaryLength</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>clubhouseStyle</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>recordAttendance</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>legendaryPlayer</v>
       </c>
     </row>
     <row r="2">
@@ -938,35 +4916,95 @@
       <c r="E2" t="str">
         <v>England</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G2">
         <v>1814</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>30000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>51.5156</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-0.1244</v>
       </c>
-      <c r="J2" t="str">
+      <c r="K2" t="str">
         <v>Thomas Lord</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Grass</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
+        <v>#0B5A31</v>
+      </c>
+      <c r="N2" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Home of Cricket,MCC Headquarters,The Lord’s Slope</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>First cricket international 1877|Home of the Ashes urn</v>
+      </c>
+      <c r="R2" t="str">
         <v>Home of Cricket</v>
       </c>
-      <c r="M2" t="str">
-        <v>Historic,Tradition,MCC</v>
-      </c>
-      <c r="N2" t="str">
-        <v>First match 1877|Test cricket hub</v>
-      </c>
-      <c r="O2">
-        <v>8</v>
+      <c r="S2" t="str">
+        <v>Hosts the annual Eton v Harrow match</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Hosted 3 Cricket World Cup Finals (1975, 1979, 2019)</v>
+      </c>
+      <c r="U2">
+        <v>34</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Test / ODI</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Pavilion End &amp; Nursery End</v>
+      </c>
+      <c r="X2" t="str">
+        <v>729/6d (Australia, 1930)</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>141+ Tests (most of any ground)</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>The Lord’s Slope — 2.5m fall across the pitch, side to side</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>Balanced, slope influences swing bowling</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>No</v>
+      </c>
+      <c r="AC2">
+        <v>1884</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>Middlesex CCC</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>3 (1975, 1979, 2019)</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>~82m (short square, longer straight)</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>Victorian pavilion, members-only jacket &amp; tie dress code</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>~30,000 (sellout Test)</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>W. G. Grace &amp; Don Bradman</v>
       </c>
     </row>
     <row r="3">
@@ -974,58 +5012,439 @@
         <v>Cricket</v>
       </c>
       <c r="B3" t="str">
-        <v>IPL</v>
+        <v>Test Cricket</v>
       </c>
       <c r="C3" t="str">
+        <v>The Oval</v>
+      </c>
+      <c r="D3" t="str">
+        <v>London</v>
+      </c>
+      <c r="E3" t="str">
+        <v>England</v>
+      </c>
+      <c r="F3" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G3">
+        <v>1845</v>
+      </c>
+      <c r="H3">
+        <v>25500</v>
+      </c>
+      <c r="I3">
+        <v>51.488</v>
+      </c>
+      <c r="J3">
+        <v>-0.1263</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M3" t="str">
+        <v>#1A472A</v>
+      </c>
+      <c r="N3" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P3" t="str">
+        <v>First Test venue in England,Traditional Ashes decider,Gasholders backdrop</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>England’s first home Test, 1880</v>
+      </c>
+      <c r="R3" t="str">
+        <v>The Oval</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Traditionally hosts the final Ashes Test of English summers</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Home of Surrey CCC since 1845</v>
+      </c>
+      <c r="U3">
+        <v>35</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Test / ODI</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Pavilion End &amp; Vauxhall End</v>
+      </c>
+      <c r="X3" t="str">
+        <v>903/7d (England vs Australia, 1938)</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>100+ Tests</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>First Test venue in England (1880)</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>Traditionally pace-friendly</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AC3">
+        <v>1880</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>Surrey CCC</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Hosted 2019 World Cup opening match</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>~75-85m</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>Victorian pavilion with historic gasholders backdrop</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>~26,000</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>Jack Hobbs</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Cricket</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Test Cricket</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Melbourne Cricket Ground</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="F4" t="str">
+        <v>🇦🇺</v>
+      </c>
+      <c r="G4">
+        <v>1854</v>
+      </c>
+      <c r="H4">
+        <v>100024</v>
+      </c>
+      <c r="I4">
+        <v>-37.8167</v>
+      </c>
+      <c r="J4">
+        <v>144.9833</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M4" t="str">
+        <v>#003366</v>
+      </c>
+      <c r="N4" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Largest stadium in the Southern Hemisphere,Boxing Day Test,First-ever Test match venue</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Hosted the first Test match ever, 1877</v>
+      </c>
+      <c r="R4" t="str">
+        <v>The MCG</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Boxing Day Test tradition since 1950</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Hosted 2015 Cricket World Cup Final</v>
+      </c>
+      <c r="U4">
+        <v>57</v>
+      </c>
+      <c r="V4" t="str">
+        <v>Test / ODI / T20</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Members End &amp; Great Southern Stand End</v>
+      </c>
+      <c r="X4" t="str">
+        <v>624 (Australia, high-scoring drop-in pitch)</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>~120 Tests</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Boxing Day Test tradition since 1950</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>Drop-in pitch, traditionally pace-friendly</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>Yes (pioneered day-night Tests, 2015)</v>
+      </c>
+      <c r="AC4">
+        <v>1877</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>Victoria (Sheffield Shield)</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>2 (1992 semi-final host venue, 2015 Final)</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>~90-100m (largest cricket boundary in the world)</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>Members’ Long Room, largest stadium in Australia</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>~100,024 (Boxing Day Test record)</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>Don Bradman</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Cricket</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Test Cricket</v>
+      </c>
+      <c r="C5" t="str">
         <v>Eden Gardens</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D5" t="str">
         <v>Kolkata</v>
       </c>
-      <c r="E3" t="str">
+      <c r="E5" t="str">
         <v>India</v>
       </c>
-      <c r="F3">
+      <c r="F5" t="str">
+        <v>🇮🇳</v>
+      </c>
+      <c r="G5">
         <v>1934</v>
       </c>
-      <c r="G3">
-        <v>68000</v>
-      </c>
-      <c r="H3">
-        <v>22.5651</v>
-      </c>
-      <c r="I3">
-        <v>88.3828</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Historic Design</v>
-      </c>
-      <c r="K3" t="str">
+      <c r="H5">
+        <v>66349</v>
+      </c>
+      <c r="I5">
+        <v>22.5674</v>
+      </c>
+      <c r="J5">
+        <v>88.3664</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L5" t="str">
         <v>Grass</v>
       </c>
-      <c r="L3" t="str">
-        <v>Castle of Cricket</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Passionate crowds,Historic,India</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Test victories|IPL finals</v>
-      </c>
-      <c r="O3">
-        <v>9</v>
+      <c r="M5" t="str">
+        <v>#FF6B1B</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Largest cricket stadium in India,1987 World Cup Final,Passionate crowds</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>1996 World Cup semi-final crowd incident</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Eden Gardens</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Hosted the 1987 Cricket World Cup Final</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Home of Bengal cricket &amp; Kolkata Knight Riders (IPL)</v>
+      </c>
+      <c r="U5">
+        <v>58</v>
+      </c>
+      <c r="V5" t="str">
+        <v>Test / ODI / T20</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Pavilion End &amp; Club House End</v>
+      </c>
+      <c r="X5" t="str">
+        <v>India 724/9d-class totals on subcontinent-friendly pitches</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>~40 Tests</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>1996 World Cup semi-final crowd riot forced a forfeit</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>Turning, spin-friendly</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>Yes (India’s first day-night Test, 2019)</v>
+      </c>
+      <c r="AC5">
+        <v>1934</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>Bengal &amp; Kolkata Knight Riders (IPL)</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>1 (1987 Final)</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>~65-70m</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>Colonial-era pavilion, historically India’s largest-capacity ground</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>~100,000 (historic, safety-capped to ~66,000 since)</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>Sourav Ganguly</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>Cricket</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Test Cricket</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Sydney Cricket Ground</v>
+      </c>
+      <c r="D6" t="str">
+        <v>Sydney</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="F6" t="str">
+        <v>🇦🇺</v>
+      </c>
+      <c r="G6">
+        <v>1848</v>
+      </c>
+      <c r="H6">
+        <v>48625</v>
+      </c>
+      <c r="I6">
+        <v>-33.8917</v>
+      </c>
+      <c r="J6">
+        <v>151.225</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L6" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M6" t="str">
+        <v>#003366</v>
+      </c>
+      <c r="N6" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O6" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P6" t="str">
+        <v>New Year Test tradition,Heritage-listed pavilions,Bodyline series host</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>Host of the 1932-33 Bodyline series matches</v>
+      </c>
+      <c r="R6" t="str">
+        <v>The SCG</v>
+      </c>
+      <c r="S6" t="str">
+        <v>New Year’s Test tradition each January</v>
+      </c>
+      <c r="T6" t="str">
+        <v>Home of New South Wales cricket since 1848</v>
+      </c>
+      <c r="U6">
+        <v>59</v>
+      </c>
+      <c r="V6" t="str">
+        <v>Test / ODI / T20</v>
+      </c>
+      <c r="W6" t="str">
+        <v>Randwick End &amp; Paddington End</v>
+      </c>
+      <c r="X6" t="str">
+        <v>659/8d (Australia)</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>~60 Tests</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>New Year’s Test tradition (early January)</v>
+      </c>
+      <c r="AA6" t="str">
+        <v>Spin-friendly, especially late in the match</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AC6">
+        <v>1882</v>
+      </c>
+      <c r="AD6" t="str">
+        <v>New South Wales (Sheffield Shield)</v>
+      </c>
+      <c r="AE6" t="str">
+        <v>0 finals (hosted group/semi-final matches)</v>
+      </c>
+      <c r="AF6" t="str">
+        <v>~70-80m</v>
+      </c>
+      <c r="AG6" t="str">
+        <v>Heritage-listed Members’ and Ladies’ Pavilions</v>
+      </c>
+      <c r="AH6" t="str">
+        <v>~48,000</v>
+      </c>
+      <c r="AI6" t="str">
+        <v>Steve Waugh (emotional SCG farewell Test, 2004)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AI6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:AJ5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1044,34 +5463,97 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="P1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="R1" t="str">
         <v>nickname</v>
       </c>
-      <c r="M1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="T1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="U1" t="str">
         <v>collectorNumber</v>
+      </c>
+      <c r="V1" t="str">
+        <v>surfaceType</v>
+      </c>
+      <c r="W1" t="str">
+        <v>grandSlamName</v>
+      </c>
+      <c r="X1" t="str">
+        <v>courtName</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>retractableRoof</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>numberOfCourts</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>recordAttendance</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>mostTitlesMale</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>mostTitlesFemale</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>prizeMoneyTotal</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>firstEditionYear</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>signatureTradition</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>traditionalAttire</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>nightSessionCapable</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>longestMatchRecord</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>queueTradition</v>
       </c>
     </row>
     <row r="2">
@@ -1090,35 +5572,98 @@
       <c r="E2" t="str">
         <v>England</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G2">
         <v>1877</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>15000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>51.4347</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-0.2157</v>
       </c>
-      <c r="J2" t="str">
-        <v>Historic Design</v>
-      </c>
       <c r="K2" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L2" t="str">
         <v>Grass</v>
       </c>
-      <c r="L2" t="str">
-        <v>Mecca of Tennis</v>
-      </c>
       <c r="M2" t="str">
-        <v>Grand Slam,Grass courts,Tradition</v>
+        <v>#006B3E</v>
       </c>
       <c r="N2" t="str">
-        <v>First Grand Slam 1877|Murray 2013</v>
-      </c>
-      <c r="O2">
-        <v>10</v>
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Oldest tennis tournament in the world,All-white dress code,Strawberries &amp; cream</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>First-ever Grand Slam tournament, 1877</v>
+      </c>
+      <c r="R2" t="str">
+        <v>The Championships</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Only Grand Slam still played on grass</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Federer &amp; Djokovic share the men’s record of 8 titles</v>
+      </c>
+      <c r="U2">
+        <v>36</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Wimbledon</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Centre Court</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Yes (Centre Court 2009, No.1 Court 2019)</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>18 championship courts</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>~15,000 (Centre Court capacity)</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Roger Federer &amp; Novak Djokovic (8 each)</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Martina Navratilova (9)</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>~£50 million (2023)</v>
+      </c>
+      <c r="AE2">
+        <v>1877</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>Strawberries &amp; cream, all-white dress code</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>Mandatory all-white clothing</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>Limited (11pm curfew)</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>Isner vs Mahut, 11hr 5min over 3 days (2010)</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>Yes — famous "The Queue" for ground passes</v>
       </c>
     </row>
     <row r="3">
@@ -1129,55 +5674,338 @@
         <v>US Open</v>
       </c>
       <c r="C3" t="str">
-        <v>USTA National Tennis Center</v>
+        <v>USTA Billie Jean King National Tennis Center</v>
       </c>
       <c r="D3" t="str">
         <v>New York</v>
       </c>
       <c r="E3" t="str">
-        <v>USA</v>
-      </c>
-      <c r="F3">
+        <v>United States</v>
+      </c>
+      <c r="F3" t="str">
+        <v>🇺🇸</v>
+      </c>
+      <c r="G3">
         <v>1978</v>
       </c>
-      <c r="G3">
-        <v>24000</v>
-      </c>
       <c r="H3">
-        <v>40.7589</v>
+        <v>23771</v>
       </c>
       <c r="I3">
-        <v>-73.8204</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Modern Design</v>
+        <v>40.7282</v>
+      </c>
+      <c r="J3">
+        <v>-73.8326</v>
       </c>
       <c r="K3" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="L3" t="str">
         <v>Hard court</v>
       </c>
-      <c r="L3" t="str">
+      <c r="M3" t="str">
+        <v>#0066CC</v>
+      </c>
+      <c r="N3" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Largest tennis stadium in the world,Electric night-session atmosphere,Highest prize money in tennis</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Arthur Ashe Stadium opened 1997, first retractable roof added 2016</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Flushing Meadows</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Only Grand Slam using a final-set tiebreak at 6-6</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Serena Williams 6 Open-era women’s titles</v>
+      </c>
+      <c r="U3">
+        <v>37</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Hard court (DecoTurf)</v>
+      </c>
+      <c r="W3" t="str">
+        <v>US Open</v>
+      </c>
+      <c r="X3" t="str">
         <v>Arthur Ashe Stadium</v>
       </c>
-      <c r="M3" t="str">
-        <v>Grand Slam,Hard court,American</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Serena dominance|Nadal records</v>
-      </c>
-      <c r="O3">
-        <v>11</v>
+      <c r="Y3" t="str">
+        <v>Yes (installed 2016)</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>22+ courts</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>23,771 (Ashe Stadium — largest tennis venue in the world)</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Jimmy Connors &amp; Roger Federer (5 each, Open era)</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>Chris Evert &amp; Serena Williams (6 each, Open era)</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>~$65 million (2023, highest in tennis)</v>
+      </c>
+      <c r="AE3">
+        <v>1881</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Night session under lights with loud New York crowd energy</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>No dress code</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>Yes (signature primetime night sessions)</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>Multiple epic 5-setters, no extended final-set rule</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>No formal queue tradition</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Tennis</v>
+      </c>
+      <c r="B4" t="str">
+        <v>French Open</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Roland Garros</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E4" t="str">
+        <v>France</v>
+      </c>
+      <c r="F4" t="str">
+        <v>🇫🇷</v>
+      </c>
+      <c r="G4">
+        <v>1891</v>
+      </c>
+      <c r="H4">
+        <v>15000</v>
+      </c>
+      <c r="I4">
+        <v>48.8466</v>
+      </c>
+      <c r="J4">
+        <v>2.2477</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Clay</v>
+      </c>
+      <c r="M4" t="str">
+        <v>#FF6B6B</v>
+      </c>
+      <c r="N4" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Rafael Nadal’s 14 titles,Red clay tradition,Slowest Grand Slam surface</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Nadal’s unmatched 14 French Open titles (2005-2022)</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Roland Garros</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Court Philippe-Chatrier roof added 2020</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Nadal 14 titles — most by any player at a single Slam</v>
+      </c>
+      <c r="U4">
+        <v>60</v>
+      </c>
+      <c r="V4" t="str">
+        <v>Clay (red clay)</v>
+      </c>
+      <c r="W4" t="str">
+        <v>French Open</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Court Philippe-Chatrier</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Yes (installed 2020)</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>20 courts</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>~15,000 (Court Philippe-Chatrier)</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>Rafael Nadal (14 — a record margin unmatched at any Slam)</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>Chris Evert (7)</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>~€49 million (2023)</v>
+      </c>
+      <c r="AE4">
+        <v>1891</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>Red clay stains on players’ whites, longer rallies</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>No strict dress code</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>Yes (since roof/lights added)</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>Notable 5-hour+ 5-setters, clay slows play down</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>No</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Tennis</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Australian Open</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Australian Open Courts</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Melbourne</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Australia</v>
+      </c>
+      <c r="F5" t="str">
+        <v>🇦🇺</v>
+      </c>
+      <c r="G5">
+        <v>1905</v>
+      </c>
+      <c r="H5">
+        <v>15000</v>
+      </c>
+      <c r="I5">
+        <v>-37.8721</v>
+      </c>
+      <c r="J5">
+        <v>144.9808</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Modern</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Hard Court</v>
+      </c>
+      <c r="M5" t="str">
+        <v>#0066CC</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P5" t="str">
+        <v>"The Happy Slam" nickname,First Slam with a retractable roof,Extreme heat matches</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Djokovic-Nadal 2012 Final — longest Grand Slam final ever (5hr 53min)</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Melbourne Park</v>
+      </c>
+      <c r="S5" t="str">
+        <v>First Grand Slam of the tennis calendar year</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Novak Djokovic 10 titles (record)</v>
+      </c>
+      <c r="U5">
+        <v>61</v>
+      </c>
+      <c r="V5" t="str">
+        <v>Hard court (GreenSet/Plexicushion)</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Australian Open</v>
+      </c>
+      <c r="X5" t="str">
+        <v>Rod Laver Arena</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Yes — first Grand Slam venue with one (1988)</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>8 show courts plus outer courts</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>~15,000 (Rod Laver Arena)</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>Novak Djokovic (10)</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>Margaret Court (11, spanning pre/post-Open eras) / Serena Williams (7 Open-era)</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>~A$76.5 million (2023)</v>
+      </c>
+      <c r="AE5">
+        <v>1905</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>Extreme Heat Policy, relaxed "Happy Slam" atmosphere</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>No dress code</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>Yes (matches often finish past midnight)</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>Djokovic vs Nadal, 2012 Final, 5hr 53min (longest Slam final)</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>No</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:AJ5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1196,34 +6024,97 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="P1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="R1" t="str">
         <v>nickname</v>
       </c>
-      <c r="M1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="T1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="U1" t="str">
         <v>collectorNumber</v>
+      </c>
+      <c r="V1" t="str">
+        <v>parTotal</v>
+      </c>
+      <c r="W1" t="str">
+        <v>courseLength</v>
+      </c>
+      <c r="X1" t="str">
+        <v>numberOfHoles</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>signatureHole</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>courseStyle</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>majorChampionship</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>recordScore</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>legendaryChampion</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>clubhouseStyle</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>membershipType</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>notableHazard</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>firstTournamentYear</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>traditionSymbol</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>greenSpeed</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>seasonPlayed</v>
       </c>
     </row>
     <row r="2">
@@ -1242,35 +6133,98 @@
       <c r="E2" t="str">
         <v>Scotland</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>🏴󠁧󠁢󠁳󠁣󠁴󠁿</v>
+      </c>
+      <c r="G2">
         <v>1552</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>40000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>56.3903</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-2.7933</v>
       </c>
-      <c r="J2" t="str">
-        <v>Natural course</v>
-      </c>
       <c r="K2" t="str">
+        <v>Natural course (no single designer)</v>
+      </c>
+      <c r="L2" t="str">
         <v>Links grass</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
+        <v>#004B87</v>
+      </c>
+      <c r="N2" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#D4AF37</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Oldest golf course in the world,Home of Golf,Most-hosted Open venue</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>First Open Championship played here, 1873</v>
+      </c>
+      <c r="R2" t="str">
         <v>Home of Golf</v>
       </c>
-      <c r="M2" t="str">
-        <v>Oldest course,Historic,Links</v>
-      </c>
-      <c r="N2" t="str">
-        <v>First tournament 1873|Tiger wins</v>
-      </c>
-      <c r="O2">
-        <v>12</v>
+      <c r="S2" t="str">
+        <v>Hosted The Open more than any other course (30+ times)</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Jack Nicklaus won here twice (1970, 1978)</v>
+      </c>
+      <c r="U2">
+        <v>38</v>
+      </c>
+      <c r="V2">
+        <v>72</v>
+      </c>
+      <c r="W2" t="str">
+        <v>6,721 yards</v>
+      </c>
+      <c r="X2">
+        <v>18</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>17th "Road Hole" — famous bunker and road hazard</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Links</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>The Open Championship (hosted 30+ times, most of any course)</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Low 60s under calm links conditions (varies by year/weather)</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Old Tom Morris &amp; Jack Nicklaus (2 Opens each here)</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>R&amp;A Clubhouse — iconic grey stone building beside the 18th green</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>Public (St Andrews Links Trust)</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>Road Hole Bunker (17th) &amp; Hell Bunker (14th)</v>
+      </c>
+      <c r="AG2">
+        <v>1873</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>Claret Jug (Open Championship trophy)</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>~10-11 stimpmeter (weather-dependent links speed)</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>July (Open Championship week)</v>
       </c>
     </row>
     <row r="3">
@@ -1278,7 +6232,7 @@
         <v>Golf</v>
       </c>
       <c r="B3" t="str">
-        <v>Masters Tournament</v>
+        <v>US Masters</v>
       </c>
       <c r="C3" t="str">
         <v>Augusta National Golf Club</v>
@@ -1287,49 +6241,332 @@
         <v>Augusta</v>
       </c>
       <c r="E3" t="str">
-        <v>USA</v>
-      </c>
-      <c r="F3">
+        <v>United States</v>
+      </c>
+      <c r="F3" t="str">
+        <v>🇺🇸</v>
+      </c>
+      <c r="G3">
         <v>1933</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>30000</v>
       </c>
-      <c r="H3">
-        <v>33.5028</v>
-      </c>
       <c r="I3">
-        <v>-82.0138</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Bobby Jones</v>
+        <v>33.5038</v>
+      </c>
+      <c r="J3">
+        <v>-82.0224</v>
       </c>
       <c r="K3" t="str">
-        <v>Championship grass</v>
+        <v>Bobby Jones &amp; Alister MacKenzie</v>
       </c>
       <c r="L3" t="str">
-        <v>The Masters</v>
+        <v>Bermuda / bentgrass greens</v>
       </c>
       <c r="M3" t="str">
-        <v>Green jacket,Prestige,Tradition</v>
+        <v>#003312</v>
       </c>
       <c r="N3" t="str">
-        <v>Tiger comeback 2019|Nicklaus era</v>
-      </c>
-      <c r="O3">
-        <v>13</v>
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#DAA520</v>
+      </c>
+      <c r="P3" t="str">
+        <v>The Masters,Green Jacket tradition,Azaleas in bloom every April</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Tiger Woods’ record-breaking 1997 debut win by 12 strokes</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Augusta</v>
+      </c>
+      <c r="S3" t="str">
+        <v>The only major played at the same course every year</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Jack Nicklaus 6 Masters titles (record)</v>
+      </c>
+      <c r="U3">
+        <v>39</v>
+      </c>
+      <c r="V3">
+        <v>72</v>
+      </c>
+      <c r="W3" t="str">
+        <v>7,545 yards</v>
+      </c>
+      <c r="X3">
+        <v>18</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Amen Corner (holes 11-13)</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>Parkland</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>The Masters (founding home course since 1934)</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>-20 (Jordan Spieth 2015, Tiger Woods 1997, Dustin Johnson 2020)</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>Jack Nicklaus (6 wins) &amp; Tiger Woods (5 wins)</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>Colonial white clubhouse, strictly private and exclusive</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Private (invitation-only)</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Rae’s Creek fronting the 12th green</v>
+      </c>
+      <c r="AG3">
+        <v>1934</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>Green Jacket</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>~13-14 stimpmeter (among the fastest greens in golf)</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>April (Masters week)</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Golf</v>
+      </c>
+      <c r="B4" t="str">
+        <v>PGA Championship</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Pebble Beach Golf Links</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Pebble Beach</v>
+      </c>
+      <c r="E4" t="str">
+        <v>United States</v>
+      </c>
+      <c r="F4" t="str">
+        <v>🇺🇸</v>
+      </c>
+      <c r="G4">
+        <v>1919</v>
+      </c>
+      <c r="H4">
+        <v>10000</v>
+      </c>
+      <c r="I4">
+        <v>36.5271</v>
+      </c>
+      <c r="J4">
+        <v>-121.9496</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Jack Neville &amp; Douglas Grant</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Bentgrass/Poa annua</v>
+      </c>
+      <c r="M4" t="str">
+        <v>#228B22</v>
+      </c>
+      <c r="N4" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Pacific coastline holes,Multiple US Open host,AT&amp;T Pro-Am celebrity field</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Tiger Woods’ record 15-stroke US Open win, 2000</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Pebble Beach</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Hosts the annual AT&amp;T Pebble Beach Pro-Am</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Jack Nicklaus &amp; Tiger Woods both won US Opens here</v>
+      </c>
+      <c r="U4">
+        <v>62</v>
+      </c>
+      <c r="V4">
+        <v>72</v>
+      </c>
+      <c r="W4" t="str">
+        <v>6,828 yards</v>
+      </c>
+      <c r="X4">
+        <v>18</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>7th (shortest hole, cliffside par-3) &amp; 18th (iconic Pacific-side closer)</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Links / coastal</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>US Open (hosted multiple times)</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>Historically tough US Open setup — winning scores often near even par</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>Jack Nicklaus &amp; Tiger Woods (2000, 15-shot record win)</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>The Lodge at Pebble Beach — luxury resort clubhouse</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>Public (resort course)</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>Pacific Ocean cliffs along multiple holes</v>
+      </c>
+      <c r="AG4">
+        <v>1929</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>Iconic 18th-hole Pacific coastline photograph (first major event: 1929 US Amateur)</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>~11-12 stimpmeter</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>June (US Open) / February (AT&amp;T Pro-Am)</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Golf</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Open Championship</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Turnberry</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Turnberry</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Scotland</v>
+      </c>
+      <c r="F5" t="str">
+        <v>🏴󠁧󠁢󠁳󠁣󠁴󠁿</v>
+      </c>
+      <c r="G5">
+        <v>1906</v>
+      </c>
+      <c r="H5">
+        <v>10000</v>
+      </c>
+      <c r="I5">
+        <v>55.3435</v>
+      </c>
+      <c r="J5">
+        <v>-4.9045</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Historic (Ailsa Course)</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Links grass</v>
+      </c>
+      <c r="M5" t="str">
+        <v>#004B87</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Iconic lighthouse landmark,1977 "Duel in the Sun",Coastal links course</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>1977 "Duel in the Sun" — Tom Watson beat Jack Nicklaus by one shot</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Turnberry</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Served as an RAF airfield during both World Wars</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Tom Watson’s 1977 Open win over Nicklaus</v>
+      </c>
+      <c r="U5">
+        <v>63</v>
+      </c>
+      <c r="V5">
+        <v>70</v>
+      </c>
+      <c r="W5" t="str">
+        <v>7,354 yards</v>
+      </c>
+      <c r="X5">
+        <v>18</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>9th "Bruce’s Castle" — played across the water with the lighthouse behind</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>Links</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>The Open Championship</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>63 (Greg Norman, 1986)</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>Tom Watson (1977 &amp; 1994 Open wins)</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>Turnberry Lighthouse landmark, luxury resort hotel</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>Public (resort course)</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>Coastal winds and cliffside rough near the lighthouse</v>
+      </c>
+      <c r="AG5">
+        <v>1977</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>Turnberry Lighthouse</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>~10-11 stimpmeter</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>July</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:AJ5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1348,34 +6585,97 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="P1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="R1" t="str">
         <v>nickname</v>
       </c>
-      <c r="M1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="T1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="U1" t="str">
         <v>collectorNumber</v>
+      </c>
+      <c r="V1" t="str">
+        <v>pitchDimensions</v>
+      </c>
+      <c r="W1" t="str">
+        <v>roofType</v>
+      </c>
+      <c r="X1" t="str">
+        <v>recordAttendance</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>homeUnion</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>tryLineTradition</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>grandSlamsWon</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>worldCupFinalsHosted</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>rivalryFixture</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>famousStand</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>floodlightsInstalled</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>singingTradition</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>firstMatchYear</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>governingBody</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>highestScoreRecord</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>legendaryPlayer</v>
       </c>
     </row>
     <row r="2">
@@ -1394,47 +6694,440 @@
       <c r="E2" t="str">
         <v>England</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G2">
         <v>1907</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>82000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>51.4545</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-0.3394</v>
       </c>
-      <c r="J2" t="str">
-        <v>Archibald Leitch</v>
-      </c>
       <c r="K2" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L2" t="str">
         <v>Grass</v>
       </c>
-      <c r="L2" t="str">
-        <v>Fortress England</v>
-      </c>
       <c r="M2" t="str">
-        <v>Rugby HQ,Historic,England home</v>
+        <v>#FFFFFF</v>
       </c>
       <c r="N2" t="str">
-        <v>1999 World Cup|England Grand Slams</v>
-      </c>
-      <c r="O2">
-        <v>14</v>
+        <v>#FF0000</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Home of England Rugby,Largest dedicated rugby stadium in the world,"Swing Low" anthem</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>England’s 2003 Rugby World Cup homecoming celebrations</v>
+      </c>
+      <c r="R2" t="str">
+        <v>HQ</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Hosted the 2015 Rugby World Cup Final</v>
+      </c>
+      <c r="T2" t="str">
+        <v>England 13 Five/Six Nations Grand Slams</v>
+      </c>
+      <c r="U2">
+        <v>40</v>
+      </c>
+      <c r="V2" t="str">
+        <v>144m x 70m (incl. in-goal areas)</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Partial (all four stands covered, open centre)</v>
+      </c>
+      <c r="X2" t="str">
+        <v>82,000 (regular sellouts)</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>England Rugby (RFU)</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>"Swing Low, Sweet Chariot" sung by the crowd</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>England 13 Five/Six Nations Grand Slams</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>1 (2015 Rugby World Cup Final)</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Calcutta Cup vs Scotland / vs Wales</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>The West Stand</v>
+      </c>
+      <c r="AE2">
+        <v>1995</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>"Swing Low, Sweet Chariot" match-day anthem</v>
+      </c>
+      <c r="AG2">
+        <v>1909</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>Rugby Football Union (owns freehold)</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>England’s biggest home Six Nations wins over Italy and Wales</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>Jonny Wilkinson</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Rugby</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Rugby Championship</v>
+      </c>
+      <c r="C3" t="str">
+        <v>Eden Park</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Auckland</v>
+      </c>
+      <c r="E3" t="str">
+        <v>New Zealand</v>
+      </c>
+      <c r="F3" t="str">
+        <v>🇳🇿</v>
+      </c>
+      <c r="G3">
+        <v>1913</v>
+      </c>
+      <c r="H3">
+        <v>50000</v>
+      </c>
+      <c r="I3">
+        <v>-37.1859</v>
+      </c>
+      <c r="J3">
+        <v>174.7654</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M3" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="N3" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P3" t="str">
+        <v>All Blacks fortress,Haka performed before kickoff,Longest unbeaten home run in rugby</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>All Blacks unbeaten at Eden Park since 1994</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Rugby HQ (NZ)</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Hosted both the 1987 and 2011 Rugby World Cup Finals</v>
+      </c>
+      <c r="T3" t="str">
+        <v>All Blacks’ longest single-venue unbeaten streak in world rugby</v>
+      </c>
+      <c r="U3">
+        <v>41</v>
+      </c>
+      <c r="V3" t="str">
+        <v>~148m x 100m (oval, multi-sport ground)</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Open air</v>
+      </c>
+      <c r="X3" t="str">
+        <v>60,000+ (historic peak, now capped near 50,000)</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>New Zealand All Blacks</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>Haka (Ka Mate) performed before kickoff</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>N/A (Rugby Championship format has no Grand Slam)</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>2 (1987, 2011 Rugby World Cup Finals)</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>All Blacks vs Australia (Bledisloe Cup)</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>ASB Stand</v>
+      </c>
+      <c r="AE3">
+        <v>1996</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>Opponents’ Haka-response traditions</v>
+      </c>
+      <c r="AG3">
+        <v>1914</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>Eden Park Trust</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>All Blacks unbeaten at Eden Park since 1994 — longest single-venue unbeaten run in rugby history</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>Richie McCaw</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Rugby</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Rugby World Cup</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Murrayfield Stadium</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Edinburgh</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Scotland</v>
+      </c>
+      <c r="F4" t="str">
+        <v>🏴󠁧󠁢󠁳󠁣󠁴󠁿</v>
+      </c>
+      <c r="G4">
+        <v>1925</v>
+      </c>
+      <c r="H4">
+        <v>67144</v>
+      </c>
+      <c r="I4">
+        <v>55.9425</v>
+      </c>
+      <c r="J4">
+        <v>-3.2355</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M4" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="N4" t="str">
+        <v>#0066CC</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Home of Scotland Rugby,"Flower of Scotland" pre-match roar,Largest stadium in Scotland</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Scotland’s 1990 Grand Slam decider vs England — the iconic slow walk-out</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Murrayfield</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Co-hosted matches at the 1991 and 2007 Rugby World Cups</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Scotland 3 Grand Slams (1925, 1984, 1990)</v>
+      </c>
+      <c r="U4">
+        <v>64</v>
+      </c>
+      <c r="V4" t="str">
+        <v>144m x 70m</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Open air</v>
+      </c>
+      <c r="X4" t="str">
+        <v>104,000 (1975 vs Wales, pre-modern-seating era)</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Scotland Rugby (SRU)</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>"Flower of Scotland" sung passionately pre-match</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>Scotland 3 Grand Slams (1925, 1984, 1990)</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>0 (hosted pool/knockout matches in 1991 &amp; 2007)</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>Calcutta Cup vs England</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>East Stand</v>
+      </c>
+      <c r="AE4">
+        <v>1994</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>"Flower of Scotland" match-day anthem</v>
+      </c>
+      <c r="AG4">
+        <v>1925</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>Scottish Rugby Union</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>1990 Grand Slam decider vs England (13-7)</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>Gavin Hastings</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Rugby</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Rugby World Cup</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Millennium Stadium</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Cardiff</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Wales</v>
+      </c>
+      <c r="F5" t="str">
+        <v>🏴󠁧󠁢󠁷󠁬󠁳󠁿</v>
+      </c>
+      <c r="G5">
+        <v>1999</v>
+      </c>
+      <c r="H5">
+        <v>74500</v>
+      </c>
+      <c r="I5">
+        <v>51.4785</v>
+      </c>
+      <c r="J5">
+        <v>-3.1823</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Bligh Lobb Sports Architecture</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Grass</v>
+      </c>
+      <c r="M5" t="str">
+        <v>#FF0000</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P5" t="str">
+        <v>First UK stadium with a fully retractable roof,Home of Wales Rugby,"Hymns and Arias" singing</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Wales’ Grand Slam-clinching wins under a closed roof</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Principality Stadium (renamed 2016)</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Hosted 1999 Rugby World Cup pool and knockout matches</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Wales multiple Grand Slams since 1999 (2005, 2008, 2012, 2019)</v>
+      </c>
+      <c r="U5">
+        <v>65</v>
+      </c>
+      <c r="V5" t="str">
+        <v>144m x 70m</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Fully retractable — first in UK rugby</v>
+      </c>
+      <c r="X5" t="str">
+        <v>74,500 (regular sellouts)</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Wales Rugby (WRU)</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>"Hymns and Arias" — Welsh crowd singing tradition</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>Wales multiple Grand Slams since 1999 (2005, 2008, 2012, 2019)</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>0 (hosted 1999 RWC pool/knockout matches)</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>Wales vs England</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>North Stand</v>
+      </c>
+      <c r="AE5">
+        <v>1999</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>Welsh hymn singing &amp; "Land of My Fathers" anthem</v>
+      </c>
+      <c r="AG5">
+        <v>1999</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>Welsh Rugby Union</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>Wales’ Grand Slam-clinching victories under the closed roof</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>Gareth Edwards</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:AJ5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1453,34 +7146,97 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="P1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="R1" t="str">
         <v>nickname</v>
       </c>
-      <c r="M1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="T1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="U1" t="str">
         <v>collectorNumber</v>
+      </c>
+      <c r="V1" t="str">
+        <v>gamesEdition</v>
+      </c>
+      <c r="W1" t="str">
+        <v>eventsHosted</v>
+      </c>
+      <c r="X1" t="str">
+        <v>openingCeremonyHeld</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>closingCeremonyHeld</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>torchCauldronLocation</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>medalsAwarded</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>legacyUseToday</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>legendaryAthlete</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>architecturalStyle</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>recordsSetHere</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>constructionCost</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>capacityDuringGames</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>renovatedSince</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>sustainabilityFeatures</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>hostCityLegacy</v>
       </c>
     </row>
     <row r="2">
@@ -1491,7 +7247,7 @@
         <v>Summer Olympics</v>
       </c>
       <c r="C2" t="str">
-        <v>Estadio Nacional de Beijing</v>
+        <v>Beijing National Stadium</v>
       </c>
       <c r="D2" t="str">
         <v>Beijing</v>
@@ -1499,47 +7255,440 @@
       <c r="E2" t="str">
         <v>China</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
+        <v>🇨🇳</v>
+      </c>
+      <c r="G2">
         <v>2008</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>91000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>39.9942</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>116.4074</v>
       </c>
-      <c r="J2" t="str">
-        <v>Herzog and de Meuron</v>
-      </c>
       <c r="K2" t="str">
+        <v>Herzog &amp; de Meuron with Ai Weiwei</v>
+      </c>
+      <c r="L2" t="str">
         <v>Track and field</v>
       </c>
-      <c r="L2" t="str">
-        <v>Bird's Nest</v>
-      </c>
       <c r="M2" t="str">
-        <v>Architecture,Beijing 2008,Modern</v>
+        <v>#DE2910</v>
       </c>
       <c r="N2" t="str">
-        <v>Bolt records|Phelps 8 golds</v>
-      </c>
-      <c r="O2">
-        <v>15</v>
+        <v>#FFD700</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Only stadium to host both Summer &amp; Winter Olympic ceremonies,Steel lattice "Bird’s Nest" design,Bolt’s world records</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Usain Bolt’s 100m (9.69s) and 200m (19.30s) world records, 2008</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Bird’s Nest</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Reused for 2022 Winter Olympics opening/closing ceremonies</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Unique dual Summer + Winter Olympic host venue</v>
+      </c>
+      <c r="U2">
+        <v>42</v>
+      </c>
+      <c r="V2" t="str">
+        <v>2008 Beijing Summer Olympics</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Athletics, Opening &amp; Closing Ceremonies</v>
+      </c>
+      <c r="X2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Mounted on the stadium roof rim, lit by Li Ning "running" around the structure</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>~102 athletics gold-medal events</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Reused for 2022 Winter Olympics ceremonies — first venue for both Games</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Usain Bolt (100m/200m world records, 2008)</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>Steel lattice "bird’s nest" design by Herzog &amp; de Meuron / Ai Weiwei</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>Bolt’s 100m (9.69s) and 200m (19.30s) world records</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>~$480 million USD</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>91,000 (reduced to ~80,000 post-Games)</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>2022 (Winter Olympics reuse)</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>Rainwater collection and natural ventilation design</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>Now a dual Summer + Winter Olympic venue, hosts tours and events</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Olympic Venues</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Summer Olympics</v>
+      </c>
+      <c r="C3" t="str">
+        <v>London Olympic Stadium</v>
+      </c>
+      <c r="D3" t="str">
+        <v>London</v>
+      </c>
+      <c r="E3" t="str">
+        <v>England</v>
+      </c>
+      <c r="F3" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G3">
+        <v>2012</v>
+      </c>
+      <c r="H3">
+        <v>66000</v>
+      </c>
+      <c r="I3">
+        <v>51.5381</v>
+      </c>
+      <c r="J3">
+        <v>0.0163</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Populous</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Track and field</v>
+      </c>
+      <c r="M3" t="str">
+        <v>#0055B8</v>
+      </c>
+      <c r="N3" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="P3" t="str">
+        <v>"Legacy-first" design built for post-Games reduction,"Super Saturday" 2012 athletics,Now West Ham United’s home</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>"Super Saturday" — three British athletics golds in one hour, 2012</v>
+      </c>
+      <c r="R3" t="str">
+        <v>London Stadium</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Converted into a Premier League football ground in 2016</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Model for legacy-first Olympic stadium design worldwide</v>
+      </c>
+      <c r="U3">
+        <v>43</v>
+      </c>
+      <c r="V3" t="str">
+        <v>2012 London Summer Olympics</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Athletics, Opening &amp; Closing Ceremonies</v>
+      </c>
+      <c r="X3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>204 copper petals forming a cauldron at the centre of the stadium (Heatherwick design)</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>~47 athletics gold-medal events</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Now West Ham United’s home ground (London Stadium)</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>Mo Farah — 5000m/10000m "double-double" begun here in 2012</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>Lightweight design engineered for post-Games size reduction</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>Mo Farah’s 5000m/10000m gold double, 2012</v>
+      </c>
+      <c r="AF3" t="str">
+        <v>~£429 million</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>80,000 (reduced to 60,000 post-Games as London Stadium)</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>2016 (football conversion for West Ham)</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>Demountable upper tier and reduced steel use versus prior Olympic stadiums</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>Became the template for "legacy-first" Olympic stadium design</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Olympic Venues</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Summer Olympics</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Tokyo Olympic Stadium</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Tokyo</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Japan</v>
+      </c>
+      <c r="F4" t="str">
+        <v>🇯🇵</v>
+      </c>
+      <c r="G4">
+        <v>2019</v>
+      </c>
+      <c r="H4">
+        <v>68000</v>
+      </c>
+      <c r="I4">
+        <v>35.6754</v>
+      </c>
+      <c r="J4">
+        <v>139.7514</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Kengo Kuma</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Track</v>
+      </c>
+      <c r="M4" t="str">
+        <v>#E74C3C</v>
+      </c>
+      <c r="N4" t="str">
+        <v>#3498DB</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Timber from all 47 Japanese prefectures,Held with no spectators due to COVID-19,Replaced the historic 1964 stadium</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Delayed 2020 Games held in 2021 under pandemic restrictions</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Japan National Stadium</v>
+      </c>
+      <c r="S4" t="str">
+        <v>First Olympic Games held with no spectators in the stadium</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Built on the same site as the 1964 Tokyo Olympic Stadium</v>
+      </c>
+      <c r="U4">
+        <v>66</v>
+      </c>
+      <c r="V4" t="str">
+        <v>2020 Tokyo Summer Olympics (held 2021)</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Athletics, Opening &amp; Closing Ceremonies</v>
+      </c>
+      <c r="X4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Large flower-shaped cauldron, later moved outside for public viewing</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>~48 athletics gold-medal events</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>Used for athletics events and occasional rugby/concerts</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>Elaine Thompson-Herah — sprint double-double, 2021</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>Wood-and-green design by Kengo Kuma using timber from all 47 Japanese prefectures</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>Held during COVID-19 with no in-venue spectators — unique in Olympic history</v>
+      </c>
+      <c r="AF4" t="str">
+        <v>~$1.4 billion USD</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>68,000</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>2019 (new build, replaced the 1964 stadium)</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>Extensive sustainable Japanese timber and natural cross-ventilation</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>Replaced the original 1964 Tokyo Olympics stadium on the same site</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Olympic Venues</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Summer Olympics</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Paris La Défense Arena</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Paris</v>
+      </c>
+      <c r="E5" t="str">
+        <v>France</v>
+      </c>
+      <c r="F5" t="str">
+        <v>🇫🇷</v>
+      </c>
+      <c r="G5">
+        <v>2017</v>
+      </c>
+      <c r="H5">
+        <v>8000</v>
+      </c>
+      <c r="I5">
+        <v>48.8955</v>
+      </c>
+      <c r="J5">
+        <v>2.2393</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Christian de Portzamparc</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Arena (temporary pool for Games)</v>
+      </c>
+      <c r="M5" t="str">
+        <v>#003DA5</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Europe’s largest indoor arena,Largest temporary Olympic pool ever built,"Use existing venues" sustainability model</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Léon Marchand’s home-Games swimming golds, 2024</v>
+      </c>
+      <c r="R5" t="str">
+        <v>La Défense Arena</v>
+      </c>
+      <c r="S5" t="str">
+        <v>Home of Racing 92 rugby club outside Games time</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Centrepiece of Paris 2024’s existing-venue sustainability strategy</v>
+      </c>
+      <c r="U5">
+        <v>67</v>
+      </c>
+      <c r="V5" t="str">
+        <v>2024 Paris Summer Olympics</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Swimming, Water Polo finals</v>
+      </c>
+      <c r="X5" t="str">
+        <v>No (opening ceremony was staged on the Seine River)</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>No (Stade de France hosted the closing ceremony)</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>N/A — cauldron was a hot-air-balloon design at the Tuileries Garden</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>~35 swimming gold-medal events</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>Home of Racing 92 rugby club; Europe’s largest indoor arena</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>Léon Marchand — home-Games swimming star</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>Modern multi-purpose indoor arena, largest in Europe by capacity</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>Housed the largest temporary Olympic swimming pool ever installed</v>
+      </c>
+      <c r="AF5" t="str">
+        <v>~€360 million (2017 build)</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>~15,000 (reduced from 40,000 max for the pool configuration)</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>2024 (temporary Olympic conversion)</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>Reused an existing arena rather than building new, central to Paris 2024’s sustainability pledge</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>Demonstrated Paris 2024's existing-venue-first sustainability strategy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O2"/>
+  <dimension ref="A1:AJ5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1558,34 +7707,97 @@
         <v>country</v>
       </c>
       <c r="F1" t="str">
+        <v>countryFlag</v>
+      </c>
+      <c r="G1" t="str">
         <v>opened</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>capacity</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>lat</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>lng</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>architect</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>surface</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
+        <v>colourThemePrimary</v>
+      </c>
+      <c r="N1" t="str">
+        <v>colourThemeSecondary</v>
+      </c>
+      <c r="O1" t="str">
+        <v>colourThemeAccent</v>
+      </c>
+      <c r="P1" t="str">
+        <v>famousFor</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>iconicMoments</v>
+      </c>
+      <c r="R1" t="str">
         <v>nickname</v>
       </c>
-      <c r="M1" t="str">
-        <v>famousFor</v>
-      </c>
-      <c r="N1" t="str">
-        <v>iconicMoments</v>
-      </c>
-      <c r="O1" t="str">
+      <c r="S1" t="str">
+        <v>notableEvents</v>
+      </c>
+      <c r="T1" t="str">
+        <v>championshipHistory</v>
+      </c>
+      <c r="U1" t="str">
         <v>collectorNumber</v>
+      </c>
+      <c r="V1" t="str">
+        <v>venueType</v>
+      </c>
+      <c r="W1" t="str">
+        <v>biggestFightHosted</v>
+      </c>
+      <c r="X1" t="str">
+        <v>recordAttendance</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>ringSize</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>legendaryBoxer</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>titlesDefended</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>knockoutRecord</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>promoterAssociation</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>broadcastHistory</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>capacityForBoxing</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>firstFightYear</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>walkoutTradition</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>notableRivalry</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>arenaNickname</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>otherEventsHosted</v>
       </c>
     </row>
     <row r="2">
@@ -1602,42 +7814,435 @@
         <v>New York</v>
       </c>
       <c r="E2" t="str">
-        <v>USA</v>
-      </c>
-      <c r="F2">
+        <v>United States</v>
+      </c>
+      <c r="F2" t="str">
+        <v>🇺🇸</v>
+      </c>
+      <c r="G2">
         <v>1968</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>20000</v>
       </c>
-      <c r="H2">
+      <c r="I2">
         <v>40.7505</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>-73.9934</v>
       </c>
-      <c r="J2" t="str">
-        <v>Modern Design</v>
-      </c>
       <c r="K2" t="str">
+        <v>Charles Luckman</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Boxing ring</v>
+      </c>
+      <c r="M2" t="str">
+        <v>#001F3F</v>
+      </c>
+      <c r="N2" t="str">
+        <v>#FF4136</v>
+      </c>
+      <c r="O2" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P2" t="str">
+        <v>"The World’s Most Famous Arena",Ali vs Frazier "Fight of the Century",Boxing’s spiritual home</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>Ali vs Frazier I — "Fight of the Century", 1971</v>
+      </c>
+      <c r="R2" t="str">
+        <v>The Garden</v>
+      </c>
+      <c r="S2" t="str">
+        <v>Hosts NBA Knicks and NHL Rangers outside fight nights</v>
+      </c>
+      <c r="T2" t="str">
+        <v>World title fights across every weight class since 1925 (current building since 1968)</v>
+      </c>
+      <c r="U2">
+        <v>44</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Indoor arena (4th iteration of MSG)</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Ali vs Frazier I, "Fight of the Century" (1971)</v>
+      </c>
+      <c r="X2" t="str">
+        <v>~20,455</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Standard 20ft ring (24ft outer apron)</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Muhammad Ali</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>World title fights across every weight class since 1925</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>Documented individually per fight — no single standing record</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>Historically Top Rank and Madison Square Garden Boxing</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>Ali-Frazier I was among the highest-grossing closed-circuit broadcasts of its era</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>~20,000 (vs 20,789 for basketball/hockey configuration)</v>
+      </c>
+      <c r="AF2">
+        <v>1925</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>Historic ring-walk theatre, varies by era and fighter</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>Ali vs Frazier trilogy (Fight I held here)</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>The World’s Most Famous Arena</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>NBA Knicks, NHL Rangers, major concerts</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Boxing</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Title Fights</v>
+      </c>
+      <c r="C3" t="str">
+        <v>O2 Arena</v>
+      </c>
+      <c r="D3" t="str">
+        <v>London</v>
+      </c>
+      <c r="E3" t="str">
+        <v>England</v>
+      </c>
+      <c r="F3" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G3">
+        <v>2000</v>
+      </c>
+      <c r="H3">
+        <v>20000</v>
+      </c>
+      <c r="I3">
+        <v>51.5054</v>
+      </c>
+      <c r="J3">
+        <v>0.0053</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Richard Rogers</v>
+      </c>
+      <c r="L3" t="str">
+        <v>Boxing ring</v>
+      </c>
+      <c r="M3" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="N3" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O3" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P3" t="str">
+        <v>UK’s busiest boxing arena,Anthony Joshua’s rise to world titles,Matchroom Boxing headquarters venue</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>Multiple Anthony Joshua heavyweight world title defences</v>
+      </c>
+      <c r="R3" t="str">
+        <v>The O2</v>
+      </c>
+      <c r="S3" t="str">
+        <v>Regular Sky Sports Box Office headline venue</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Home venue for Matchroom Boxing’s biggest UK cards</v>
+      </c>
+      <c r="U3">
+        <v>45</v>
+      </c>
+      <c r="V3" t="str">
         <v>Indoor arena</v>
       </c>
-      <c r="L2" t="str">
-        <v>The Garden</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Boxing history,Title fights,Iconic</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Ali vs Frazier 1971|Tyson fights</v>
-      </c>
-      <c r="O2">
-        <v>16</v>
+      <c r="W3" t="str">
+        <v>Anthony Joshua world title defences (multiple)</v>
+      </c>
+      <c r="X3" t="str">
+        <v>~20,000</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Standard 20ft ring</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>Anthony Joshua</v>
+      </c>
+      <c r="AA3" t="str">
+        <v>Multiple heavyweight and world title fights since the 2000s</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>Varies by fight — no single standing venue record</v>
+      </c>
+      <c r="AC3" t="str">
+        <v>Matchroom Boxing (Eddie Hearn)</v>
+      </c>
+      <c r="AD3" t="str">
+        <v>Regular Sky Sports Box Office headline venue</v>
+      </c>
+      <c r="AE3" t="str">
+        <v>~20,000</v>
+      </c>
+      <c r="AF3">
+        <v>2000</v>
+      </c>
+      <c r="AG3" t="str">
+        <v>Elaborate entrance productions in the Joshua era</v>
+      </c>
+      <c r="AH3" t="str">
+        <v>Anthony Joshua’s rise-to-the-top fights held here</v>
+      </c>
+      <c r="AI3" t="str">
+        <v>The Dome</v>
+      </c>
+      <c r="AJ3" t="str">
+        <v>Concerts, NBA London games</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Boxing</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Title Fights</v>
+      </c>
+      <c r="C4" t="str">
+        <v>Caesars Palace</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Las Vegas</v>
+      </c>
+      <c r="E4" t="str">
+        <v>United States</v>
+      </c>
+      <c r="F4" t="str">
+        <v>🇺🇸</v>
+      </c>
+      <c r="G4">
+        <v>1966</v>
+      </c>
+      <c r="H4">
+        <v>4296</v>
+      </c>
+      <c r="I4">
+        <v>36.1138</v>
+      </c>
+      <c r="J4">
+        <v>-115.1728</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Historic</v>
+      </c>
+      <c r="L4" t="str">
+        <v>Boxing ring</v>
+      </c>
+      <c r="M4" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="N4" t="str">
+        <v>#000000</v>
+      </c>
+      <c r="O4" t="str">
+        <v>#FF6B00</v>
+      </c>
+      <c r="P4" t="str">
+        <v>Defined the 1980s Las Vegas boxing boom,Hagler vs Hearns "The War",Historic outdoor car-park arena fights</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>Hagler vs Hearns — one of the most explosive fights in history, lasting under 8 minutes (1985)</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Caesars Palace Sports Pavilion</v>
+      </c>
+      <c r="S4" t="str">
+        <v>Hosted the peak of the "Caesars Palace era" of 1970s-80s boxing</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Numerous 1970s-80s world title bouts staged in its outdoor pavilion</v>
+      </c>
+      <c r="U4">
+        <v>68</v>
+      </c>
+      <c r="V4" t="str">
+        <v>Casino outdoor arena (historic temporary setup)</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Ali vs Spinks II (1978), Hagler vs Hearns (1985)</v>
+      </c>
+      <c r="X4" t="str">
+        <v>~15,000 (outdoor temporary era)</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Standard 20ft ring</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Marvin Hagler &amp; Sugar Ray Leonard</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>Numerous 1970s-80s world title bouts ("Caesars Palace era" of boxing)</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>Hagler-Hearns lasted under 8 minutes — one of the most explosive fights in history</v>
+      </c>
+      <c r="AC4" t="str">
+        <v>Bob Arum &amp; Don King (historic era)</v>
+      </c>
+      <c r="AD4" t="str">
+        <v>Defined the Las Vegas pay-per-view boxing boom of the 1980s</v>
+      </c>
+      <c r="AE4" t="str">
+        <v>~15,000 (outdoor temporary configuration)</v>
+      </c>
+      <c r="AF4">
+        <v>1972</v>
+      </c>
+      <c r="AG4" t="str">
+        <v>N/A — outdoor temporary-era fights</v>
+      </c>
+      <c r="AH4" t="str">
+        <v>Hagler vs Hearns "The War" (1985)</v>
+      </c>
+      <c r="AI4" t="str">
+        <v>Caesars Palace Sports Pavilion</v>
+      </c>
+      <c r="AJ4" t="str">
+        <v>Concerts and high-roller entertainment events</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>Boxing</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Title Fights</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Wembley Stadium Boxing</v>
+      </c>
+      <c r="D5" t="str">
+        <v>London</v>
+      </c>
+      <c r="E5" t="str">
+        <v>England</v>
+      </c>
+      <c r="F5" t="str">
+        <v>🏴󠁧󠁢󠁥󠁮󠁧󠁿</v>
+      </c>
+      <c r="G5">
+        <v>2019</v>
+      </c>
+      <c r="H5">
+        <v>90000</v>
+      </c>
+      <c r="I5">
+        <v>51.5559</v>
+      </c>
+      <c r="J5">
+        <v>-0.2795</v>
+      </c>
+      <c r="K5" t="str">
+        <v>Populous</v>
+      </c>
+      <c r="L5" t="str">
+        <v>Boxing ring</v>
+      </c>
+      <c r="M5" t="str">
+        <v>#003DA5</v>
+      </c>
+      <c r="N5" t="str">
+        <v>#FFFFFF</v>
+      </c>
+      <c r="O5" t="str">
+        <v>#FFD700</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Anthony Joshua vs Wladimir Klitschko 2017,One of the highest-attended boxing events of the modern era,Football stadium converted for boxing</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>Joshua knocked down then stopped Klitschko in round 11 — an instant classic (2017)</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Wembley Stadium</v>
+      </c>
+      <c r="S5" t="str">
+        <v>England football internationals and the FA Cup Final are also held here</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Multiple heavyweight world title unifications staged here</v>
+      </c>
+      <c r="U5">
+        <v>69</v>
+      </c>
+      <c r="V5" t="str">
+        <v>Outdoor stadium (football ground converted for fight night)</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Anthony Joshua vs Wladimir Klitschko (2017, 90,000 attendance)</v>
+      </c>
+      <c r="X5" t="str">
+        <v>90,000 (Joshua vs Klitschko, 2017)</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Standard 20ft ring, elevated for stadium sightlines</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>Anthony Joshua</v>
+      </c>
+      <c r="AA5" t="str">
+        <v>Multiple heavyweight world title unifications</v>
+      </c>
+      <c r="AB5" t="str">
+        <v>Joshua knocked down then stopped Klitschko in round 11 (2017) — regarded as an instant classic</v>
+      </c>
+      <c r="AC5" t="str">
+        <v>Matchroom Boxing</v>
+      </c>
+      <c r="AD5" t="str">
+        <v>One of the highest-attended boxing events of the modern era in the UK</v>
+      </c>
+      <c r="AE5" t="str">
+        <v>~90,000 (stadium configuration)</v>
+      </c>
+      <c r="AF5">
+        <v>2017</v>
+      </c>
+      <c r="AG5" t="str">
+        <v>Grand stadium entrance productions</v>
+      </c>
+      <c r="AH5" t="str">
+        <v>Anthony Joshua vs Wladimir Klitschko</v>
+      </c>
+      <c r="AI5" t="str">
+        <v>Wembley Stadium</v>
+      </c>
+      <c r="AJ5" t="str">
+        <v>England football internationals, FA Cup Final, major concerts</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ5"/>
   </ignoredErrors>
 </worksheet>
 </file>